--- a/校园招聘/制造业/消费电子／通信／智能设备/生产物流类/质量工程师/2_保留题目/4轮_消费电子／通信／智能设备_质量工程师_可保留的题目.xlsx
+++ b/校园招聘/制造业/消费电子／通信／智能设备/生产物流类/质量工程师/2_保留题目/4轮_消费电子／通信／智能设备_质量工程师_可保留的题目.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:S50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,6 +513,3975 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>请简单说说，为什么手机外壳的尺寸公差和表面划痕会被列为关键质量特性？</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>因为这两项直接影响用户对产品外观与装配功能的直观感知，且在量产过程中易受模具磨损、注塑参数波动、装配夹具偏移及物流搬运等过程因素影响，一旦超差将直接导致整机装配干涉、缝隙不均或客户批量投诉，必须纳入质量控制计划中优先监控。</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>实际工作中，通常采用三种方式识别其关键性：一是结合客户投诉TOP问题清单与售后返修数据反向锁定高频失效项；二是依据DFMEA中严重度评分≥8且发生频度≥4的失效模式，将其对应的尺寸和外观特性标定为关键；三是通过产线首件比对与分层审核时发现的重复性偏差趋势，动态更新关键特性清单。其中，第一种方式响应最快，适用于新品上市初期快速聚焦；第二种更系统但依赖前期开发输入完整性；第三种最贴近现场，但滞后于问题发生。当前产线导入阶段，推荐以客户投诉+DFMEA双源交叉验证的方式最稳妥。</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：客户批量拒收某批次外壳，但尺寸检测报告全部合格。具体情况：公差带内尺寸组合叠加后导致与中框装配时局部干涉，而单点尺寸未超差。解决思路：立即启动尺寸链分析，联合结构工程师复核关键配合面的尺寸方向性与公差累积路径，在控制计划中补充‘尺寸方向性标注’和‘装配模拟验证’要求。1个复杂问题概要：表面划痕缺陷率在不同产线间波动大，且同一台设备早中晚班次差异显著。具体问题：划痕位置随机、无规律，常规巡检无法定位根本原因。解决思路：启用基于图像识别的在线表面缺陷分类看板，同步采集设备参数（如机械手抓取力度、传送带速度、治具清洁频次）做多因子相关性分析，锁定‘治具微颗粒残留’与‘清洁周期超2小时’的强关联，推动建立治具清洁点检与防错验证机制。</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>质量基础判定</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>质量对象识别</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>关键质量特性识别</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>请简单说说，电子制造中常见的‘功能失效’和‘外观不良’这两类缺陷，通常分别对应哪两个主要的缺陷等级？</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>在消费电子通信智能设备制造业的质量工程师日常判定中，功能失效通常对应严重缺陷等级，外观不良通常对应轻微缺陷等级。这一划分依据是企业通用的缺陷等级分类规则，即以缺陷对产品安全、基本使用功能、客户核心体验及合规性的影响程度为根本判定标准。</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>实际作业中，质量工程师常用四种判定路径：一是直接引用客户特定标准，如某头部手机品牌明确将无法开机列为A级（严重），而边框微划痕列为C级（轻微），该方法响应快但需动态更新客户清单；二是沿用公司内部《缺陷等级判定基准书》中按失效机理归类的映射表，稳定高效，但若未及时同步新机型结构变化易滞后；三是结合过程能力数据辅助校准，例如某产线连续三批出现同一外观问题但无客诉，则可推动升级为一般缺陷，但依赖数据闭环时效性；四是跨职能协同会签机制，在开发阶段由质量、研发、客服共同评审新缺陷场景并预设等级，前瞻性好但耗时较长。当前量产阶段最管用的是第二种，即严格依据已受控发布的判定基准书执行，兼顾效率与合规。</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：客户临时提高某外观项判定标准，导致原定轻微缺陷被要求按一般缺陷管控。具体情况：某智能手表表带喷漆颗粒在量产初期按轻微等级放行，但上市后因竞品对标升级，客户邮件要求将其纳入一般缺陷管理。解决思路：立即启动客户标准变更识别流程，比对新版《客户特殊要求清单》，同步更新内部判定基准书并完成相关岗位培训，同时对库存及在制批次开展分级追溯评估。1个复杂问题概要：同一缺陷在不同产品形态下等级归属不一致。具体问题：同一种PCB焊点虚焊，在TWS耳机中导致蓝牙断连属功能失效（严重），但在智能手环中仅影响非核心传感器精度，客户接受为一般缺陷。解决思路：建立‘缺陷-产品-应用场景’三维判定矩阵，由先期质量工程师牵头在项目APQP阶段完成映射固化，并嵌入PPAP文件包作为后续量产判定唯一依据。</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>质量基础判定</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>缺陷判定规则</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>缺陷等级分类</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>某智能手表整机在包装出货前抽检发现表带扣合处存在轻微间隙，但功能测试、防水测试和跌落测试全部合格。作为质量判定人员，你需在4小时内决定是否放行该批次。请简述你会重点识别并验证哪些关键质量特性，并说明这些特性如何影响用户实际使用体验和长期质量风险。</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>聚焦表带扣合结构的装配完整性、尺寸匹配性、锁止可靠性及外观一致性四项关键质量特性；确认其是否属于设计定义的特殊特性或客户明示的外观/装配类KPC；核查该间隙是否超出企业内控标准及客户接收准则中的允许限值。</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>第一种做法是快速调取该型号的DFMEA/PFMEA文件与控制计划，比对扣合部位是否被识别为安全/法规相关或感知质量高敏感度特性——适用于开发资料完整、变更受控的成熟机型，但若为新平台首单则可能因FMEA未覆盖而漏判；第二种是组织跨职能现场复现评估，邀请产线装配工、客服代表、终端用户代表共同进行佩戴模拟与日常使用场景推演——时效性强且贴近真实体验，但若缺乏标准化评价指引易导致主观偏差；第三种是调用历史客诉数据库检索同类间隙问题的退换率、返修率及保修期内失效模式分布——数据支撑力强，但对全新型号或无售后数据的批次不适用；当前4小时时限下，应优先采用第二种加第一种组合方式，在保证决策时效的同时兼顾技术依据与用户视角。</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：间隙未超图纸公差但高频出现在同一装配工位。具体情况：该现象指向过程能力不足或夹具磨损，非单纯来料问题。解决思路：立即暂停该工位后续产出，启动分层审核锁定人机料法环变量，同步更新巡检频次与首件确认项。1个复杂问题概要：客户未明确定义该间隙的接收标准，但竞品普遍无可见间隙。具体问题：缺乏量化依据支撑放行与否，易引发客户质量争议与品牌感知落差。解决思路：基于感知质量评价模型（如QFD权重矩阵）组织小样本盲测，结合客户质量协议中‘合理预期’条款形成书面判定依据，并同步推动设计端将该间隙纳入下一版外观基准样板与检验指导书。</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>质量基础判定</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>质量对象识别</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>关键质量特性识别</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>请简述消费电子整机装配过程中，螺丝漏打或打滑可能引发的质量风险。</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>螺丝漏打或打滑属于装配过程中的基础装配失效，直接导致产品结构完整性、功能可靠性及外观一致性三类质量对象异常：结构上可能引发部件松动、脱落或受力失衡；功能上可能造成屏蔽失效、接地不良、散热异常或运动机构卡滞；外观上易出现螺钉头凸起、凹陷、划伤或明显空位等可视缺陷。</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>在实际质量管控中，常用四种作业方法识别和应对该风险：一是首件确认时结合BOM与扭矩图逐项核对关键螺丝点位与状态，适用于新机型导入阶段，但依赖作业员经验，易在多型号混线时漏判；二是过程巡检采用‘目视+手感+抽检扭力’组合方式，覆盖量产稳定性要求，但对微小滑牙或隐性漏打敏感度不足；三是分层审核中由班组长及以上角色按装配工位清单执行‘点位打卡式’核查，强化责任追溯，但若审核表未动态更新变更点则存在滞后风险；四是依托防错工装（如带感应反馈的电动螺丝刀）实时拦截异常，时效性最强且数据可追溯，但需供应商协同验证工装有效性，前期导入周期较长。当前产线最管用的是第三种与第四种方法的组合应用。</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：螺丝漏打被漏检流入下工序。具体情况：某批次手机中框与主板支架连接处漏打一颗M1.6螺丝，因该点位无视觉标识且不在首检必查项中，巡检未覆盖，导致整机跌落测试时支架断裂。解决思路：将该螺丝点位纳入特殊特性清单，升级为强制首件拍照比对项，并在分层审核表中增加‘隐蔽点位双人复核’动作。1个复杂问题概要：同一螺丝位反复出现打滑但扭力值达标。具体情况：某平板电脑散热模组固定螺丝连续三批出现滑牙，但电批显示扭力合格，实测发现螺丝材质批次性软化与孔位攻牙深度偏差叠加所致。解决思路：联动先期质量与量产SQE，启动来料金属成分快速筛查+孔位尺寸SPC趋势分析，同步推动设计端评估替代紧固方案并更新PPAP控制计划。</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>质量基础判定</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>质量对象识别</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>基础质量风险判断</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>请简述在电子制造中，AQL抽样检验里的‘一般检验水准II’通常适用于哪类质量检查场景？</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>一般检验水准II适用于消费电子通信智能设备制造业中，对常规量产阶段来料、半成品及成品的日常接收检验，且历史质量表现稳定、供应商过程受控、无重大变更或风险升级时的质量判定场景。</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>实际工作中有四种常用调整方式：一是当新导入供应商或首批量产时，会临时升至水准III以强化把关，但易增加检验成本和交付压力；二是对高价值或功能安全相关物料（如基带芯片、电源管理模块），即使水准II也需叠加关键特性全检，否则可能漏判致命缺陷；三是当连续多批次出现轻微波动时，会启动加严检验切换机制，但若未同步更新检验指导书版本，现场易执行错档；四是针对贴片类标准件（如阻容感、连接器），采用水准II配合C=0接收准则，兼顾效率与风险，是当前产线最常用、最平衡的做法。</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：检验水准误用为‘默认档’。具体情况：工程师未评估供应商近期质量趋势与过程变更状态，对刚经历工艺切换的模组仍沿用水准II，导致批量性外观划伤漏检。解决思路：将水准选择嵌入来料检验任务触发逻辑，系统自动关联供应商近三个月PPM、审核结果及工程变更单状态，强制校验后方可生成检验方案。1个复杂问题概要：多层级供应链下水准适用性断层。具体问题：ODM厂按水准II验收模组，但其上游模组厂对PCBA子板却用水准I，造成整机厂端发现功能性不良时追溯困难、责任界定模糊。解决思路：在新项目质量协议中明确‘链路一致性要求’，规定同一技术路径下的关键组装层级必须采用相同或更严检验水准，并通过APQP阶段联合评审固化到各阶检验标准中。</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>检验抽样基础</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>AQL抽样检验</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>抽样水准理解</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>某批次智能手表整机在跌落测试后，表带卡扣处出现0.3mm微裂纹，未贯穿且无功能影响；但AQL抽样标准规定‘外观裂纹一律拒收’，而客户签样时特别备注‘非功能区微裂纹＜0.5mm可让步接收’。你如何协调执行？请说明判定依据的优先级、需同步的关键干系人及后续标准更新建议。</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>首先确认缺陷位置属于非功能区，测量裂纹尺寸为0.3mm且未贯穿；其次明确客户签样文件为最新有效受控版本，其让步条款具有合同效力；然后依据质量判定优先级：客户特殊要求高于内部AQL标准；最后组织跨职能评审，形成让步放行决议并记录闭环。</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>常见做法有四种：一是直接按客户签样执行让步接收，适用于客户技术协议已明确定义且无历史争议场景，但若内部标准未同步更新易引发后续批量误判；二是启动临时偏差流程走ECN审批，适合涉及多批次或需留痕追溯的情况，但耗时较长可能影响交付；三是联合客户质量代表书面确认本次豁免适用性，权威性强但响应周期不可控；四是现场快速组织开发、工艺、客户质量三方短会达成共识，兼顾时效与合规，当前该单点微裂纹、非功能区、尺寸明确，此法最适用。</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：客户签样备注未加盖受控章或未纳入PLM系统受控版本。具体情况：现场查到的签样件为邮件截图或手写便签，缺乏版本号和生效日期，导致无法验证其法律效力。解决思路：立即暂停判定，联系客户质量接口人补发正式受控签样件，并同步更新内部质量文档清单索引。1个复杂问题概要：AQL标准与客户签样条款存在系统性冲突，不止本批次。具体问题：近三个月同类结构件共出现5次类似微裂纹争议，暴露内部标准未动态对标客户最新签样要求。解决思路：牵头启动质量标准基线对齐项目，梳理所有在售型号客户签样条款，修订AQL外观类缺陷判定矩阵，嵌入客户分级授权机制，并在QMS系统中设置自动预警规则。</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>质量基础判定</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>缺陷判定规则</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>判定标准理解</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>请简述，在检验一台智能音箱的整机外观时，为什么划伤、色差和装配缝隙都属于必须检查的项目？</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>因为这三项是消费电子通信智能设备制造业中整机外观类关键质量特性，直接关联客户可感知的外观一致性与装配完整性，属于先期质量策划阶段识别出的特殊外观特性，在检验抽样方案中被明确列为必检项，其判定结果直接影响整机放行决策和客户满意度评价。</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>实际作业中常用三种方法：一是依据产品外观标准样件比对判定，适用于量产稳定期且色板/间隙公差已固化的情况，但若样件老化或光照条件不统一易引发误判；二是采用分层审核机制，由巡检员、班组长、质量工程师三级复核，适合新品导入或批量爬坡阶段，但人力成本高、响应时效弱；三是结合AQL抽样+外观缺陷图谱库辅助识别，当前最常用，能兼顾效率与一致性，前提是图谱需定期更新并覆盖典型缺陷形态。综合来看，在校园招聘和社会招聘通用场景下，第三种方法最管用，既降低新人经验依赖，又符合IATF16949对检验一致性与可追溯性的要求。</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：同一台音箱在不同光照环境下划伤判定结果不一致。具体情况：产线日光灯与客户展厅LED灯色温差异导致轻微划痕显隐变化，造成内部判定合格而客户端投诉。解决思路：在检验规程中强制规定标准光源（D65）及照度范围，并将光源验证纳入首件确认清单。1个复杂问题概要：装配缝隙超差但功能正常，是否允许让步放行。具体问题：某批次音箱侧盖与顶盖缝隙达0.4mm（标准0.3mm），未影响声学性能，但客户外观评审打分低于阈值。解决思路：启动跨部门外观质量评审机制，联合开发、工艺、客户质量三方基于历史客诉数据与竞品对标结果共同决策，同步更新外观限度样板并完成PPAP变更备案。</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>检验抽样基础</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>检验项目判定</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>检验项目识别</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>某批次刚完成SMT贴片的PCBA在AOI检测后显示‘焊点桥连’不良率突然升至3.2%，但同一产线另一批次同型号PCBA的该缺陷率仍稳定在0.15%。两批次使用相同钢网、同一炉温曲线和同一批次锡膏，仅物料供应商不同（A供VS B供）。你如何快速锁定是哪个环节引入了桥连风险？请简述你的判断依据和验证顺序。</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>作为质量工程师，应立即启动变化点管理机制，将‘物料供应商切换’识别为本次异常的唯一已知变化因子；依据先期质量策划中建立的来料风险识别清单，优先确认B供物料的可制造性数据是否完成量产准入评审；同步调取该批次首件确认记录、过程巡检数据及AOI原始图像样本，比对桥连发生位置与B供元器件引脚结构、焊端共面性、表面润湿性等关键质量特性的一致性。</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>常用验证路径有四种：一是开展分层审核，聚焦B供物料上线前的来料检验执行情况与判定标准符合性，适用于来料放行流程存在执行偏差的情形，但若检验项目未覆盖共面性或氧化状态则易漏判；二是组织跨职能快速响应会，联合工艺、SQE与供应商现场复现贴片过程，适用于需验证贴片精度与元器件姿态匹配性的场景，但耗时较长，影响时效性；三是调取B供物料近三个月质量绩效趋势与变更履历，适用于供应商存在隐性制程调整但未正式通知的情形，但依赖数据完整性；当前最管用的是第一种——结合AOI图像定位桥连集中发生的元器件类型，反向追溯B供对应型号的批次级质量数据与PPAP认可状态，在4小时内完成风险聚焦。</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：B供物料虽通过初始PPAP，但未更新最新版本的可制造性验证报告。具体情况：该物料引脚镀层成分微调导致润湿速度变化，原验证未覆盖新批次锡膏与之匹配性。解决思路：立即暂停B供该物料批次使用，要求SQE协同供应商补做SMT工艺窗口验证，并更新控制计划中的来料接收准则。1个复杂问题概要：A供与B供物料在图纸规格上完全一致，但实际三维形貌存在系统性差异。具体问题：B供器件引脚共面性超差但仍在国标限值内，常规来料检验无法识别，却在高密度贴装中诱发桥连。解决思路：推动开发阶段将共面性纳入特殊特性管理，量产阶段在IQC增加抽样级3D光学检测，并将结果纳入供应商质量绩效评价维度。</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>质量基础判定</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>质量对象识别</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>基础质量风险判断</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>某通信基站模块在成品出货检验中，发现15件存在同一类型焊点虚焊，但其中8件虚焊位置位于非关键信号路径且功能测试全通过，7件位于电源路径并导致2件在老化测试中失效。AQL对‘功能影响类’和‘外观类’虚焊分别设为0.1%和2.5%，样本量200。请简述你如何结合缺陷本质、失效后果与接收准则，判定整批是否允收。</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>首先依据缺陷位置与失效表现，将15个虚焊缺陷按质量属性重新分类：8件无功能影响的归为外观类，7件已引发老化失效的归为功能影响类；其次对照AQL标准，分别核算两类缺陷在200样本中的实际比例，并与对应接收限值比对；最后综合判定——只要任一类别超标，整批即不允收。</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>实践中常用四种作业方法：一是严格按缺陷物理位置+实测后果双维度分类，适用于设计BOM与FMEA已明确关键路径的成熟产线，但若设计文档未更新或路径定义模糊时易误判；二是以老化失效结果为刚性分界，直接将所有引发失效的虚焊统一划入功能影响类，时效性强、争议少，适合交付压力大的量产场景，但可能弱化早期风险识别；三是引入过程能力趋势辅助判断，当历史批次同类缺陷呈上升趋势时主动收紧判定，利于预防批量风险，但需跨批次数据支撑，新员工或数据断档时难落地；四是联合工艺与可靠性工程师开展快速影响评估，针对边界案例做5分钟现场会签，兼顾专业性与效率，在多职能协同机制健全的团队中最管用。</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：缺陷分类归属争议。具体情况：工艺认为某电源路径虚焊未造成当前功能失效，应归外观类；而可靠性工程师指出其在高温高湿应力下必然退化，属潜在功能影响。解决思路：立即调取该模块的DFMEA和可靠性验收标准，以客户认可的失效模式定义为准，由质量工程师组织三方5分钟快速对齐，记录决策依据并同步至检验作业指导书。1个复杂问题概要：AQL标准与实际风险脱节。具体问题：客户AQL仍沿用旧版，未覆盖新型号模块中新增的低功耗待机路径失效模式，导致功能影响类缺陷实际接收限值偏松。解决思路：质量工程师牵头发起AQL适用性评审，基于近3个月市场失效数据与客户投诉趋势，提出分类细化建议（如新增‘待机功能影响类’），推动客户质量协议更新，并同步修订内部检验规程与培训材料。</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>质量基础判定</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>缺陷判定规则</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>允收拒收逻辑</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>某车载摄像头模组在制程终检中，抽样检出11处镜头镀膜划痕：其中4处位于视场边缘（光学MTF未下降），7处靠近中心区域（实测分辨率下降5%但仍在客户规格下限内）。AQL对‘影响成像性能’和‘纯外观’划痕分别设为0.65%和3.0%，样本量250。请简述你如何基于实测数据、客户规格边界及缺陷分级逻辑，决定该批是否放行。</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>首先依据客户技术协议与PPAP文件，确认划痕是否被明确定义为‘影响成像性能’类缺陷；其次结合实测数据判断中心区域7处划痕是否导致关键质量特性——即分辨率——实际偏离客户规格下限；最后按缺陷分级结果，分别套用对应AQL标准判定抽样结果是否超出接收限。</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>常见做法有四种：一是严格按缺陷分类执行双AQL判定，适用于客户规范清晰、历史数据稳定场景，但若分类依据模糊易引发跨部门争议；二是启动跨职能评审机制，联合光学设计、客户质量、工艺工程共同裁定划痕功能影响，时效略低但决策更稳健，适合首次出现或边界案例；三是调用已批准的让步放行流程，前提是已有同类缺陷的客户书面豁免记录且本次未超历史偏差幅度，否则存在合规风险；四是触发变更驱动的质量门禁复核，当发现现有缺陷分级逻辑与实测性能衰减不匹配时，需暂停放行并更新检验标准。当前最管用的是第二种，因分辨率虽未超限但已下降5%，属典型灰色地带，必须由客户质量与开发端共同确认是否构成隐性风险。</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：缺陷分级与实测性能变化不一致。具体情况：客户将中心划痕定义为‘影响成像性能’，但实测仅下降5%且仍在规格下限内，导致AQL判定与实际功能风险脱节。解决思路：立即组织客户质量接口人召开短会，以实测报告为依据，确认该衰减是否被客户接受为可容忍波动，并同步更新内部缺陷判定树。1个复杂问题概要：同一缺陷在不同客户项目中分级逻辑冲突。具体问题：某主机厂将同类中心划痕列为Critical，而另一家仅列为Major，导致量产线无法统一执行检验标准。解决思路：在供应商质量平台建立客户专属缺陷库，绑定各项目PPAP与SOR条款，所有终检判定必须调取对应客户版本的分级规则，系统强制校验后方可提交放行结论。</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>质量基础判定</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>缺陷判定规则</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>允收拒收逻辑</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>某智能音箱整机出货检验中，按AQL 0.65%正常二级抽样发现2个外观划伤和1个Wi-Fi连接失效。其中划伤集中在同一条包装线的同一工位，而Wi-Fi失效经复测确认为射频校准参数漂移。请简述该批次是否接收，并说明判定时需权衡的三个关键质量维度及其理由。</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>该批次不应接收。依据AQL 0.65%正常二级抽样方案，当样本中发现不合格品数超过接收数时，批次判拒收；本例中外观划伤属一般不合格，Wi-Fi连接失效属严重不合格，二者性质不同，须分别对照对应缺陷类别限值判定，且严重不合格一旦出现即触发拒收条件。</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>第一种做法是严格按抽样表执行，仅统计数量不区分缺陷类型——适用于历史数据稳定、过程受控的成熟产线，但本例中Wi-Fi失效属功能失效，忽略分类会掩盖系统性风险；第二种做法是分缺陷类别判定，将划伤归入一般类、Wi-Fi失效归入严重类，分别查对应接收标准——这是消费电子行业出货检验的通用做法，能兼顾效率与风险识别，当前最适用；第三种做法是结合过程信息临时升级判定，如发现划伤集中于同一工位、Wi-Fi校准漂移具批量特征，可直接启动加严检验或暂停放行——适用于已观察到过程异常信号的情形，时效性强但需有现场证据支撑，本例中两项问题均具聚集性，应优先采用。</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：抽样结果未超AQL限值，但缺陷呈现明显过程聚集。具体情况：划伤集中在同工位、Wi-Fi失效确认为校准参数漂移，表明非随机波动而是过程失控。解决思路：立即暂停该批次放行，启动过程审核与首末件比对，核查包装工位防刮措施及校准设备MSA状态，不以抽样合格为放行前提。1个复杂问题概要：严重不合格与一般不合格同时出现且成因不同。具体问题：外观划伤反映作业规范执行问题，Wi-Fi失效反映制程参数管控失效，二者需协同追溯但责任归属不同工序。解决思路：启动跨职能质量评审，由过程质量工程师牵头组织包装段与测试段联合分析，同步输出过程变更点清单与控制计划更新项，确保整改闭环覆盖所有相关控制点。</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>检验抽样基础</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>AQL抽样检验</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>批次接收判定</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>在质量分析中，如果某型号手机的主板焊接不良、屏幕划伤、电池漏液三类问题的不良率分别是0.8%、0.3%、0.1%，按改善优先级排序，应最先处理哪一类？请简单说说理由。</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>作为消费电子通信智能设备制造业的质量工程师，判断改善优先级不能仅看不良率高低，必须结合质量问题对产品安全、法规符合性、客户投诉敏感度及售后风险的实际影响程度进行综合评估。</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>实践中常用四种作业方法：一是基于严重度-发生频次-探测度的简化风险矩阵法，适用于开发与量产初期数据尚不充分时，但若过度依赖发生频次易低估低概率高后果问题；二是客户质量视角驱动法，即对照主机厂或终端品牌方的质量门禁条款和退货判定标准，对电池漏液这类触发强制召回或安规不合规项直接升级为最高优先级，时效性强且合规保障度高；三是售后失效模式回溯法，调取已上市同类机型历史客诉与返修数据，验证当前不良是否已在市场端引发批量投诉，但滞后于实际发生；四是跨职能协同评估法，联合研发、安规、客服、供应链召开快速质量评审会，形成共识性排序，适合多因交织场景。当前题干中电池漏液属安规红线问题，无论发生率多低都必须前置处理，该方法最管用。</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：将不良率数值大小直接等同于改善优先级。具体情况：现场工程师常因惯性思维优先处理主板焊接不良（0.8%），忽视电池漏液虽仅0.1%却已触发欧盟CE安规通报案例。解决思路：立即启动质量门禁核查机制，对照GB 40662、IEC 62368等强制标准条款，确认该缺陷是否属于不可接受失效模式，并同步升级至质量决策委员会备案。1个复杂问题概要：三类问题存在潜在关联性，如焊接不良导致局部过热，进而诱发电池热失控风险。具体问题：单一按表象分类排序可能掩盖系统性失效链。解决思路：采用FMEA团队复盘机制，邀请工艺、结构、电池设计代表开展失效路径推演，将电池漏液定为根本遏制点，同时将主板焊接参数纳入变更管控清单，实现源头阻断与过程受控双线并进。</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>质量数据分析</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>改善优先级判断</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>改善优先级排序</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>当来料检验发现电容、电阻、连接器三类物料的批次不合格率分别为5%、1%、0.5%，从改善效率角度出发，应优先推动哪一类物料的质量提升？请简述依据。</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>应优先推动电容类物料的质量提升。依据是：在量产SQE和开发SQE工作中，改善优先级判断需基于质量风险暴露频次与资源投入产出比的综合权衡，而非单纯看不合格率高低或技术复杂度；电容批次不合格率最高，意味着其质量波动在来料端暴露最频繁，对产线停线、返工、批次冻结等运营影响最直接，是当前质量管控中响应时效性要求最高、改进窗口最清晰的切入点。</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>实际工作中常用四种分析路径：一是按不合格率绝对值排序，适用于新供应商导入初期或数据基线尚未稳定时，但易忽略单批影响量级；二是结合物料关键特性等级（如是否为安全件、功能主控件），适用于客户投诉高频或整车功能失效关联强的情形，但需依赖先期质量策划输出，校园招聘候选人常缺乏该信息支撑；三是评估质量异常处置成本，包括检验复判、供应商协同、让步放行审批等隐性耗时，在消费电子通信智能设备制造业中，电容因用量大、型号多、替代周期短，其异常处理平均耗时显著高于电阻和连接器；四是跟踪近三个月趋势稳定性，若电容不合格率持续高于阈值且无收敛迹象，则优先级进一步强化——当前场景下，仅凭单次批次数据，第一种方法最契合新人快速上手的实操逻辑，也最符合社会招聘中对基础质量敏感度的考察意图。</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：将‘不合格率最高’直接等同于‘质量风险最大’。具体情况：电容虽批次不合格率5%，但若其为通用型贴片电容，失效模式多为参数漂移，不影响整机功能安全；而连接器虽仅0.5%，却属高速信号接口，一次失效即导致整机功能拒收。解决思路：必须回归岗位职责中的‘量产SQE方向’要求，同步调阅该物料在PPAP文件中的特性分类、在客户投诉台账中的历史问题归类及在过程审核中的关键控制点记录，交叉验证风险实质。1个复杂问题概要：多品类物料改善资源冲突下的动态优先级调整。具体问题：当电容整改刚启动，电阻突然出现批量焊盘氧化问题，引发产线集中报修。解决思路：启动量产SQE方向规定的‘变化点管理’机制，以48小时内异常上升速率、影响工序数量、客户交付节点临近程度三项运营指标重校准优先级，而非固守初始数据排序。</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>质量数据分析</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>改善优先级判断</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>改善优先级排序</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>制定纠正措施时，为什么要确保措施可验证？请简述原因。</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>因为纠正措施必须闭环落地，只有可验证，才能客观确认问题是否真正消除、措施是否真实执行、效果是否稳定受控，这是8D第八步‘防止再发生’得以成立的前提，也是质量工程师推动异常分析闭环的刚性要求。</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>在消费电子通信智能设备制造业中，常见做法有四种：一是将措施转化为具体动作加输出物，比如‘增加AOI检测程序’必须明确版本号、上线时间、首检记录；二是绑定过程参数或检验点，如将‘调整贴片机Z轴压力’对应到设备参数日志截图和SPC控制图趋势；三是采用双源交叉验证，例如既查作业员签字确认表，又调取MES工单执行轨迹；四是设置短期有效性与长期稳定性双阶验证，先看3批次合格率，再跟踪1个月过程能力。前两种适合快速响应类问题，第三种适用于跨部门协同场景，第四种最适用于涉及制程变更或供应商整改的情形，兼顾时效与可信度。</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：措施描述模糊导致验证失效。具体情况：如‘加强员工培训’未定义培训内容、对象、考核方式和验证节点，后续无法判断是否真正落实。解决思路：退回D4阶段，要求用‘谁、在什么时间、完成什么动作、产出什么证据’四要素重写措施，并由质量工程师与工艺/生产共同签字确认。1个复杂问题概要：措施本身有效但验证方式不可靠。具体问题：某FPC焊接虚焊问题，整改措施是更换焊膏型号，但仅凭首件OK就判定闭环，未同步更新来料检验标准和过程巡检频次，导致两周后同类缺陷复发。解决思路：在D5/D6阶段强制嵌入‘验证方案评审’环节，由质量工程师牵头拉通工艺、测试、SQE三方，对验证方法、样本量、判定准则、责任归属进行联合确认并留档。</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>异常分析闭环</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>8D问题解决</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>纠正措施制定</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>智能手表产线连续三批在老化测试后发现心率传感器零点漂移超差，但每批的测试设备、操作员、温湿度记录和失效数量均未统一标注。你牵头组织初步分析会前，需强制要求各环节补全哪五个不可缺失的事实要素？请简单说说。</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>必须补全时间、地点、产品批次号、失效现象具体描述、失效数量及占比这五个事实要素。时间指老化测试完成的确切日期与时段；地点指执行老化测试的具体产线工位或实验室编号；产品批次号须为唯一可追溯的制造批次标识；失效现象要明确写出零点漂移超差的实际表现，如‘静态无信号状态下输出值偏离标称零点≥0.8mV’；失效数量及占比需注明每批抽检总数、异常数量及百分比。</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>实际工作中常用四种补全方式：一是调取MES系统自动抓取批次绑定的时间戳与工位信息，适用于信息化程度高的产线，但若系统未配置老化测试工位标签则易漏项；二是由测试员现场补录结构化表单，强依赖人员责任心，若缺乏防错提示易填错或空项；三是通过测试设备日志反向提取时间与设备ID，适合有完整设备通讯记录的场景，但老旧设备可能无此功能；四是依据老化箱温湿度探头原始记录交叉锁定时段，需配套校准台账支撑，否则温湿度数据本身不可信。当前最管用的是第一种加第四种组合，既保障时效性，又通过物理环境数据形成双重时间锚点，符合消费电子行业快节奏量产问题响应要求。</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：批次号填写不一致，如混用订单号、工单号或手写简码。具体情况：同一物料在不同环节使用‘SW2405A’‘S2405-001’‘2405A-LOT’等不同标识，导致无法关联设计BOM、测试记录与返工处置单。解决思路：立即启用企业级批次编码规则检查工具，在数据录入端强制格式校验，并同步更新质量门禁清单中批次字段的必填与合规性校验逻辑。1个复杂问题概要：失效现象描述存在主观表述。具体问题：不同工程师记录为‘读数不准’‘波动大’‘偏高’等非量化语言，无法支撑后续SPC或FMEA分析。解决思路：在质量信息系统中嵌入标准化失效术语库，绑定心率传感器类器件的典型失效模式代码，要求录入时必须选择预设选项并补充实测数值，确保问题描述具备可分析性与跨团队一致性。</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>异常分析闭环</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>问题描述分类</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>问题描述五要素</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>某智能手表产线在量产爬坡阶段，连续三批整机功能测试不良率从0.3%骤升至2.1%，根本原因锁定为新导入的国产蓝牙芯片在高温高湿老化后出现间歇性断连。但该芯片已通过全部设计验证，且供应商交货周期长达12周。你作为质量负责人，在8D流程中制定纠正措施时，会如何平衡紧急出货、客户交付承诺与设计合规性？请简述你的核心决策逻辑和关键动作顺序。</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>在8D流程的D4阶段识别根本原因后，D5阶段需制定临时遏制措施，D6阶段制定永久纠正措施；必须同步启动客户沟通、跨部门协同评审与合规性评估；所有措施须基于现有质量体系文件要求执行，确保记录可追溯、决策有依据、闭环可验证。</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>常见做法有四种：一是启用备用料号切换方案，适用于已有替代芯片完成PPAP且产线已验证的情况，但若无预备案则易导致交付中断；二是实施加严全检+老化筛选，适用于短期应急且产能允许，但会显著拉低直通率并掩盖过程变异；三是推动客户签署偏差放行协议，适用于客户质量协议明确允许设计变更豁免条款的情形，否则存在合规风险；四是联合研发启动设计降级方案，如限定温湿度使用场景并更新用户手册，需经产品安全与法规团队联合评审。当前最管用的是组合策略——以加严筛选保交付、同步推进客户偏差审批、并立即启动替代方案可行性评估，三线并行确保时效性与合规性兼顾。</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：客户拒绝签署任何偏差放行，坚持原设计规格不可妥协。具体情况：客户质量协议中明确禁止未经书面批准的设计变更，且该芯片属关键通信器件。解决思路：立即组织客户质量接口人、研发、法务召开三方会议，提供老化失效数据包、历史同类案例处理记录及短期风险控制证据，推动客户启动快速变更评审通道。1个复杂问题概要：替代芯片虽已完成样品验证，但未完成量产PPAP认可。具体问题：供应商尚未提交完整PPAP文件包，且产线未做批量工艺验证。解决思路：启动PPAP加速通道，由质量工程师牵头组织开发SQE、制程工程、测试团队开展并行验证，采用分阶段文件提交+小批量试产数据补强方式，同步向客户报备PPAP进度与风险缓释计划。</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>异常分析闭环</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>8D问题解决</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>纠正措施制定</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>请简述在电子制造中，来料检验时识别元器件极性错误的常见方法。</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>作为量产SQE方向的质量工程师，需在来料检验环节系统性识别极性错误这一典型来料风险源。核心是依据图纸、规格书和封样件明确极性标识要求，在IQC检验流程中设置可视化核对、实物比对和记录追溯三个基本动作，确保极性信息与采购技术协议及PPAP提交物一致，并将识别结果纳入供应商质量绩效评价输入。</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>实际作业中常用四种方法：一是目视双人复核法，适用于标准封装如电解电容、二极管，效率高但依赖人员经验，当产线急单或夜班人力紧张时易漏判；二是极性标识比对清单法，将BOM中关键极性元器件的封装类型、标识位置、方向特征制成检查表，适配多型号混线来料，但若供应商变更封装未同步更新清单则失效；三是首件+批次抽样交叉验证法，对新供应商或设计变更后首批来料执行全检首件并记录极性判定逻辑，后续按AQL抽样复核，兼顾时效与风险覆盖，是当前主流做法；四是联合SQE与IQC开展极性识别专项培训认证，提升一线检验员对非常规标识（如丝印模糊、无标记反向贴片）的敏感度，但需配套建立典型误判案例库持续更新。</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：供应商未按图纸要求标注极性，仅靠实物外观无法判别。具体情况：某批次钽电容无极性丝印且封装对称，但规格书明确为有极性器件，IQC初检未识别即放行，导致产线焊接后批量功能失效。解决思路：立即启动来料冻结，调取该物料历史PPAP包确认极性定义条款，联合开发SQE回溯设计输入要求，同步将此风险项加入供应商来料检验强制核查清单，并在下一批次到货前完成封样件与检验标准联合确认。1个复杂问题概要：同一元器件在不同供应商间极性定义逻辑不一致。具体情况：某MCU芯片由两家供应商供货，A厂以圆点为第1脚，B厂以凹槽为第1脚，但BOM未区分来源，IQC按统一标准检验导致误判。解决思路：推动采购与SQE在SRM系统中标注供应商级极性定义差异，在来料标签增加‘极性定义源’字段，IQC扫码自动调取对应检验图示，并将该类多源器件纳入先期质量策划阶段的极性风险专项评审范围。</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>质量风险管理</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>质量风险分析</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>风险来源识别</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>在消费电子新产品试产阶段，为什么设计验证的样机数量不能少于3台？请简单说说原因。</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>因为质量工程师在先期质量策划中需识别设计验证环节的样本风险，3台是开展基本失效模式观察、验证结果交叉比对及初步稳定性判断的最低可行数量，低于该数量无法支撑对设计输出一致性的基本置信判断。</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>实际工作中常用三种处理方式：一是采用最小可行样本法，适用于高成熟度平台衍生项目，在已有充分历史数据支撑时可快速决策，但若项目存在新工艺或关键器件变更则易漏判早期失效；二是执行分层抽样验证法，按功能模块或装配批次分配样机，适合多供应商协同试产场景，但依赖前期BOM与工艺拆解精度，拆解偏差会导致风险覆盖不均；三是启动动态增量验证法，首台做功能通电验证，次台做环境应力初筛，第三台做接口兼容性与人机交互复测，该方法时效性强、职责清晰，是当前消费电子快节奏试产中最常用且稳健的做法。</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：试产仅提供2台样机且已签样放行。具体情况：研发为赶节点压缩验证资源，质量工程师未坚持样机数量底线，导致量产导入后批量出现同一结构件装配干涉问题，追溯发现单台样机未暴露该工况下的公差叠加风险。解决思路：立即冻结相关设计变更释放，组织跨部门回溯评审，补做第三台样机在极限装配条件下的实操验证，并将该情形纳入先期质量策划检查清单强制项。1个复杂问题概要：客户临时要求提前启动PPAP提交，但供应商仅交付2台工程样机。具体问题：质量工程师面临客户压力与内部验证合规性冲突，且无备用样机来源。解决思路：联合开发SQE启动供应商现场快速复刻验证流程，同步调用同平台历史项目第三台存档样机进行关键特性比对分析，形成替代性证据包，并在PPAP文件中明确标注验证局限性及闭环计划。</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>研发质量管理</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>设计验证评审</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>验证样本风险</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>某智能穿戴设备在量产阶段，供应商将PCBA上一颗关键电源管理芯片的封装形式由QFN改为WLCSP，变更已通过技术评审并下发ECN。但首批来料上线后，SMT车间反馈回流焊后该器件翘脚不良率突然升至1.2%，远超历史0.02%水平。作为质量工程师，你需立即向跨部门团队说明是否暂停使用该批物料，你会优先核查哪三个现场事实来支撑你的决策？请简述。</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>第一，核查该批WLCSP物料是否100%执行了ECN要求的变更落地动作，包括供应商是否按最新版本BOM和工艺文件供货、仓库是否完成批次隔离与标识更新；第二，核查SMT产线当前实际使用的钢网开孔参数、回流焊温度曲线及炉温实测数据是否已同步适配WLCSP封装特性；第三，核查首批上线该物料的首件确认记录、过程巡检频次与判定标准是否已针对新封装完成动态调整。</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>这三项核查分别对应变更风险识别中‘执行到位性’‘过程适配性’和‘监控有效性’三个关键维度。若仅查来料检验报告，会遗漏过程参数未切换的风险；若只看技术评审结论，会忽视现场执行断点；若依赖供应商自证，可能掩盖变更落地偏差。当前最管用的是‘三现联动核查法’：同步调取仓库ERP出库记录、SMT设备参数日志和IPQC巡检原始表单，交叉验证变更是否真实穿透到作业层。这种方法时效性强、证据链完整，避免单点信息失真；但若跨系统权限受限或记录缺失，则需启动飞行审核快速补位。</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：ECN虽已签发，但SMT车间仍沿用QFN工艺参数作业。具体情况是回流焊峰值温度和升温斜率未按WLCSP热敏感特性下调，导致芯片底部焊点润湿不均、应力集中翘脚。解决思路是立即比对新旧封装焊接工艺窗口要求，锁定参数偏差项，联合工艺工程师4小时内完成炉温曲线重设与验证。1个复杂问题概要：变更影响存在隐性传导路径。具体问题是WLCSP器件底部焊球高度公差更严，而PCB焊盘镀层厚度波动未纳入变更风险评估，造成部分板厂来料匹配度不足。解决思路是启动变化点管理机制，组织SQE、制程工程师和PCB供应商开展多源数据回溯，以首批不良品为样本反推焊盘形貌与焊球共面性匹配关系，同步升级来料接收准则。</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>质量风险管理</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>变更风险识别</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>物料变更风险</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>请简单说说：控制图上的控制限和产品规格限，各自主要用来判断什么？</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>控制限主要用于判断过程是否处于统计受控状态，即识别过程是否存在特殊原因变异；规格限主要用于判断单个产品是否符合客户或设计要求，即判定产品是否合格。</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>在消费电子通信智能设备制造业的质量工程师日常工作中，面对产线高频换型、多批次小批量、关键尺寸与功能参数波动敏感等特点，对两类限值的使用需动态适配：一是当新机种导入试产阶段，优先以控制限监控过程稳定性，避免过早用规格限误判过程能力不足；二是量产爬坡期若控制限持续收窄但不良率未降，需核查测量系统是否引入重复性偏差；三是当客户临时加严AQL或变更功能边界时，规格限调整必须同步触发控制图重置与过程能力再验证；四是分层审核中发现作业员频繁调整设备参数，此时控制限异常比规格超差更应被前置预警。其中最管用的是将控制限作为过程健康度仪表盘，规格限作为交付合规性门槛，二者不可替代也不可混用。</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：控制限内连续7点同侧排列但产品全数合格。具体情况：表面看无超规格问题，实则反映过程均值缓慢漂移，可能由治具磨损、环境温湿度累积偏移或软件校准周期失效导致，易在后续批次引发批量性功能失效。解决思路：立即暂停该工位生产，启动变化点管理流程，排查设备参数记录、环境监控数据及最近一次MSA复测结果，并结合历史控制图趋势锁定漂移起始节点。1个复杂问题概要：同一关键尺寸同时出现控制限外点和规格限内大量集中分布。具体问题：说明过程存在明显特殊原因干扰（如夹具松动），但变异方向恰好未触及规格边界，易被现场误判为‘无风险’。解决思路：质量工程师须立即组织跨职能小组开展根本原因分析，调取对应时段设备日志、操作视频与首末件比对数据，同步更新该特性的PFMEA中探测度评分，并将此场景固化为分层审核必查项。</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>制程质量控制</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SPC过程监控</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>控制限规格限区分</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>某智能穿戴设备产线对电池焊接拉力做SPC监控，控制图稳定受控，但不良率仍持续高于目标值。请简单说说，这可能反映出控制限与规格限之间存在什么典型关系，以及下一步应优先核查什么。</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>这说明过程虽统计受控，但过程能力不足，典型表现为控制限宽度远大于规格限宽度，即过程变异过大或中心偏移，导致大量数据落在规格限之外。下一步应优先核查该特性的过程能力指数CPK是否达标，并确认当前规格限设定是否合理、测量系统是否可靠。</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>实际工作中有四种常见核查路径：一是先查CPK值是否低于1.33，若偏低，说明过程固有能力不足，需聚焦设备精度、夹具稳定性或工艺参数窗口优化；二是核对规格限是否沿用早期设计值未随量产成熟度更新，尤其在智能穿戴产品迭代快的背景下，客户实际使用反馈可能已倒逼规格收紧；三是验证测量系统重复性和再现性，电池焊接拉力测试易受探针压入深度、夹持角度影响，当前MSA结果可能已失效；四是排查分层因素，比如不同批次电芯供应商来料差异是否被纳入SPC子组划分。综合来看，在消费电子产线时效压力下，应优先执行快速MSA复测和CPK快筛，这两项能在两小时内输出可行动结论。</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：规格限人为放宽未同步更新。具体情况：为保良率曾临时放宽电池焊接拉力下限，但未在FMEA和控制计划中正式修订，也未通知SPC工程师调整规格限标注，导致CPK计算失真且质量风险未暴露。解决思路：立即比对最新版工程图纸、客户CTQ清单与现场作业指导书中的规格限一致性，组织跨职能小组完成变更闭环。1个复杂问题概要：多源变异叠加掩盖真实过程能力。具体问题：同一焊接工站混用两家电芯供应商物料，但SPC子组未按供应商分层，导致控制图看似稳定，实则两个分布中心偏移叠加造成整体不良率高企。解决思路：启用分层SPC分析，按供应商、班次、设备编号等关键变化点重新归类数据，识别主导变异源后再开展针对性改善。</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>制程质量控制</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SPC过程监控</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>控制限规格限区分</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>某无线耳机充电盒组装线在盖合工序加装了压力传感器防错，当盖合不到位时设备自动停机并提示异常。但近两周出现多次停机后复位即放行、未实际校验盖合状态的情况。请简单说说你将从哪两个关键环节验证该防错措施的闭环有效性。</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>第一，验证异常触发后的处置流程是否强制执行状态确认；第二，验证复位操作前是否必须完成盖合状态的独立再验证。</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>常用验证方法有四种：一是现场跟线观察复位动作与盖合状态确认动作的时序和责任归属，适用于问题初发、人因主导场景，但若仅靠目视易漏判隐性跳过；二是调取设备人机界面操作日志与PLC状态记录做交叉比对，适用于自动化程度高、数据可追溯场景，但若日志未启用或未关联物理状态则失效；三是设置模拟异常后由不同班次操作员执行标准复位流程并录像回溯，能暴露习惯性违规，但需规避演练干扰正常生产；四是嵌入分层审核检查表，在巡检中固定抽检复位后首件的盖合功能与外观，兼顾时效与证据链完整性，当前最管用——既不中断生产，又能通过实物验证闭环落地。</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：复位操作脱离防错逻辑约束。具体情况：操作员习惯性点击复位按钮而不执行盖合状态目视/功能确认，导致停机仅为‘消警’而非‘排障’。解决思路：将复位权限与状态确认动作绑定，例如复位前须在工控屏勾选‘已确认盖合到位’并留存电子签名，同步纳入班组长分层审核必查项。1个复杂问题概要：防错系统存在‘假闭环’——设备逻辑判定异常已清除，但未与物理状态建立强关联。具体问题：压力传感器信号被屏蔽或阈值漂移后仍能触发停机，但复位后系统默认‘上次异常已解决’，未强制触发二次检测。解决思路：在复位流程中嵌入最小必要验证动作，如要求复位后自动执行一次空载盖合+压力反馈自检，并将结果写入MES工单闭环节点，确保每个停机事件对应一次可追溯的状态再确认。</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>制程质量控制</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>关键工序防错</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>防错验证逻辑</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>来料检验中发现电子元器件引脚氧化发黑，这通常归为哪一类不良？请简单说说。</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>在来料检验管理中，电子元器件引脚氧化发黑属于外观类不良中的表面状态异常，按供应商质量管理规范应归入‘来料功能性隐患类不良’，因其虽未造成即时电气失效，但直接影响后续焊接可靠性与长期服役稳定性，需按高风险外观缺陷进行判定和处置。</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>实际工作中有四种常用判定路径：一是依据IATF16949条款及客户特殊要求（如华为、小米或ODM客户对引脚氧化的AQL加严标准）直接升级为严重缺陷；二是结合来料批次历史质量趋势，若该供应商同类物料近三个月出现过三次以上类似问题，则按重复性系统性不良启动8D流程；三是对照企业内部《电子物料来料检验作业指导书》中的图像比对库，匹配氧化等级（轻度泛黄/中度发暗/重度发黑）对应不同处置方式；四是联合工艺与NPI团队做可焊性验证快筛，若24小时内完成锡球测试不合格，则立即冻结批次。其中第三种方法时效性最强、落地最稳，既避免过度升级影响交付，又防止漏判引发产线批量焊接不良。</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：检验员将引脚氧化发黑误判为一般外观瑕疵，仅做让步接收。具体情况：未识别该缺陷与回流焊空焊、虚焊的强关联性，导致后续SMT段直通率下降超15%，返工成本激增。解决思路：强制执行‘氧化类缺陷必查可焊性验证记录’的双签机制，检验员与SQE共同确认验证结果后方可放行。1个复杂问题概要：同一供应商多批次连续出现引脚氧化，但出厂检测报告全部合格。具体问题：暴露其过程防潮控制失效与出厂检验抽样代表性不足，属供应商体系运行漏洞。解决思路：启动飞行审核聚焦环境监控（温湿度记录、氮气柜压力、包装密封性）与检验方法复现性验证，同步推动其更新MSA分析并纳入年度质量协议考核项。</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>供应商质量管理</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>来料检验管理</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>来料不良分类</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>在电子制造中，来料检验发现一批手机摄像头模组的金属支架存在局部轻微划痕，不影响装配和功能，但客户标准明确要求表面无可见划伤。这类问题应归为哪一类不良？判定时除了看客户标准，还需要核对什么关键文件？</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>该问题应归为外观类不合格品，具体属于客户拒收类不良；判定时除客户标准外，还需核对双方签署的《来料检验规范》或《AQL抽样检验作业指导书》，其中必须包含该物料的接收准则、缺陷定义、判定等级及允收/拒收依据。</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>实际工作中有四种常用判定路径：一是直接依据客户签署的《外观限度样板》比对，适用于有实物封样且版本受控的情况，但若样板未更新或未覆盖当前缺陷形态则易误判；二是调取该物料最新版PPAP包中的《检验标准文件》，权威性强，但若供应商未及时提交变更后文件则存在滞后风险；三是查阅采购合同附件中的质量协议条款，法律效力高，但条款常较笼统，需结合技术文件才能落地执行；四是启动跨部门会签机制，由SQE牵头组织研发、工艺、采购共同评审，适合新发异常或标准模糊场景，但耗时较长。当前最管用的是第二条路径，因消费电子行业迭代快，PPAP文件是SOP后供应商质量能力的法定依据，且具备可追溯性与时效性。</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>异常情况概要：客户标准与内部检验标准不一致。具体情况：客户要求‘无可见划伤’，但企业现行《来料检验规范》中将‘0.5mm以下单条划痕’列为C类轻微缺陷，允收。解决思路：立即冻结该批次物料，同步核查客户标准生效日期与内部文件修订记录，确认是否因未及时升级检验标准导致系统性漏检，并在24小时内完成标准差异识别与临时控制措施备案。复杂问题概要：同一缺陷在不同客户间判定结论冲突。具体问题：该划痕被A客户拒收，但B客户同型号产品允许同等程度划痕。解决思路：建立客户专属检验矩阵表，在ERP或QMS系统中标注各客户对同类物料的差异化接收要求，并在来料检验工单生成环节自动推送对应判定基准，避免人工选择错误。</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>供应商质量管理</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>来料检验管理</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>来料不良分类</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>来料检验中，如果一批物料的包装箱上没有贴供应商批次号标签，但其他信息都齐全，这属于什么性质的问题？</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>这属于来料批次标识缺失引发的可追溯性风险问题，直接违反供应商质量管理中对批次唯一性标识的基本要求，影响来料检验结果与供应商过程的关联锁定。</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>常见处理方式有四种：一是暂停接收并启动供应商异常反馈流程，适用于首次发生且无历史合作风险记录的情况，但若紧急交付需求强易导致产线停线；二是允许开箱抽样核验实物批次号后放行，适合高信任度供应商且该物料非关键特性，但存在实物与包装信息不一致时漏判风险；三是调取供应商当批出货清单及内部批次记录进行交叉验证，需供应商配合及时响应，时效依赖协同效率；四是结合ERP/MES系统中该物料的采购订单号、送货单号反向追溯批次，当前主流制造企业普遍采用，数据链路完整时最可靠高效，是消费电子通信智能设备行业量产SQE日常首选路径。</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：供应商口头确认批次号已录入系统但未打印粘贴。具体情况：包装无标签但系统有记录，检验员误判为合规而放行，后续市场端出现同一批次功能失效却无法精准锁定范围。解决思路：立即冻结同采购订单下所有未检验批次，同步发起供应商8D中的临时遏制措施，要求其48小时内提供带批次号的纸质出货证明并完成标签补贴闭环验证。1个复杂问题概要：多级供应商嵌套导致批次号归属模糊。具体问题：模组类物料由二级供应商贴标，一级供应商仅做中转合箱，包装箱无二级供方批次号，但质量责任需追溯至源头制程。解决思路：依据前期PPAP文件中约定的标识规则，核查一级供应商《来料标识管理协议》执行情况，推动其在合箱作业中强制保留并转录原始批次号，纳入月度质量绩效评价项</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>供应商质量管理</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>来料检验管理</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>来料批次风险判断</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>RMA数据分析中，'返修设备数量'和'返修率'这两个指标分别反映什么？请简单说说。</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>返修设备数量是当期收到并进入返修流程的客户退回设备台数，直接体现售后问题的绝对发生量；返修率是返修设备数量与同期出货设备总数的比值，用于衡量产品在真实使用场景下的整体可靠性表现和客户实际体验水平。</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>在消费电子通信智能设备制造业的质量工程师日常工作中，分析这两个指标常用三种作业方法：一是按产品型号/批次/区域做交叉分层，快速定位高发问题单元，适合新品上市初期问题聚焦；二是结合RMA故障代码与维修工单结论做归因聚类，避免将不同失效机理混为一谈，适用于多品类共线生产场景；三是联动销售周期与固件版本信息做时间轴回溯，识别是否由特定软件升级或季节性环境因素引发，这对智能终端类产品尤为关键。其中，第二类方法最常用也最管用，因为消费类设备故障原因高度依赖软硬协同表现，仅看数量或比率易误判责任归属，必须紧扣故障现象与处置结论做业务归因。</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：返修数量突增但返修率未同步上升。具体情况：某批次5G模组返修设备数量周环比增长120%，但因当周恰逢大促出货激增，返修率反而下降，导致质量预警被忽略。解决思路：质量工程师需主动剥离销售波动影响，采用滚动30天出货均值作分母，并叠加首月返修占比趋势监控，确保早期异常不被稀释。1个复杂问题概要：返修率持续低于行业基准，但客户满意度评分明显下滑。具体问题：智能手表返修率仅0.8%，但大量用户因触控延迟、蓝牙断连等非硬件失效问题发起RMA，维修后仍反复退回。解决思路：质量工程师须推动建立‘有效返修’判定机制，区分功能性失效与体验型失效，在RMA系统中标注‘非硬件故障’标签，并联动研发与客服部门开展体验缺陷闭环，避免返修率失真掩盖真实质量风险。</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>客户质量管理</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>售后数据分析</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>RMA数据分析</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>客户退回一批5G模组，反馈存在间歇性信号丢失。你在8D报告第六步‘永久措施’中，如何确保所提出的改进方案既能解决当前失效，又不会引入新的装配或测试风险？请简述。</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>在第六步永久措施环节，质量工程师必须组织跨职能团队，基于根本原因验证后的整改方案，开展变更影响评估；同步更新控制计划、作业指导书和检验标准；完成小批量试产验证及客户确认；所有输出需经客户质量部门书面批准后方可量产切换。</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>常用做法有四种：一是采用变更影响矩阵表，逐项梳理对装配工位、测试工装、来料规格、过程参数和检验方法的潜在影响，适合多接口协同场景但易遗漏人因因素；二是执行FMEA驱动的再分析，聚焦新措施引入的新增失效模式，时效性强但依赖团队FMEA能力；三是启动快速分层审核，在试产阶段由质量、工艺、生产三方联合开展首件+末件+过程点检，覆盖全面但需协调资源；四是调用历史客诉数据库比对同类措施的售后表现，能预判风险但受限于数据完整性。当前最管用的是将变更影响矩阵与快速分层审核组合使用，兼顾系统性和落地性。</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：永久措施刚导入产线，客户即反馈新批次出现偶发ESD测试失败。具体情况是为解决信号丢失而加装的屏蔽罩未做接地设计变更评审，导致静电泄放路径改变。解决思路是立即冻结变更，回溯变更影响评估记录，补做EMC专项评审，并将屏蔽结构纳入供应商变更管控清单。1个复杂问题概要：客户要求永久措施须在10个工作日内闭环，但涉及模组PCB布线调整需重新送样认证。具体问题是硬件设计方拒绝开放Gerber文件，导致内部无法独立验证。解决思路是启动客户质量协同机制，由我方客户质量工程师牵头，联合客户SQE共同向供应商发起联合变更授权请求，同步启用替代验证路径——基于已通过认证的同类模组平台做等效性分析报告，经双方质量负责人签字认可后作为临时放行依据。</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>客户质量管理</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>客诉问题闭环</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>客户8D回复</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>请简述转产准入时，为什么需要确认试产阶段的客户反馈问题已全部解决？</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>因为客户反馈问题直接体现产品在真实使用场景下的质量符合性与交付可靠性，转产准入前若未闭环，意味着量产放行缺乏客户侧验证基础，不符合NPI质量策划中转产准入条件关于‘客户满意项零遗留’的刚性要求。</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>实践中常用四种作业方法：一是将客户反馈问题逐条映射至PFMEA和控制计划，确认已纳入量产控制体系，适用于问题涉及关键特性但整改周期短的情形，但若客户原始描述模糊易导致映射偏差；二是联合客户质量代表开展问题关闭联合签字确认，适用于主机厂强管控项目，但跨部门协同效率低时可能延误转产节点；三是通过客户问题清单与8D报告交叉核验闭环证据，包括整改措施、验证数据及客户书面认可，覆盖最全且可追溯，是当前消费电子通信智能设备制造业最主流、最稳妥的做法；四是调取客户售后早期预警系统（如EWS）中的同类问题趋势，辅助判断是否真闭环，适用于多型号平台复用场景，但依赖客户系统开放权限，存在信息获取壁垒。</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：客户口头确认关闭但无书面记录。具体情况：客户质量工程师在会议中表示问题已解决，但未签发正式关闭邮件或签署8D结案页，导致转产后被客户审计追溯时判定为准入失效。解决思路：质量工程师须坚持‘无书面确认不放行’原则，将客户签字/邮件作为转产准入评审材料的必备项，由先期质量组在转产门评审前完成归档校验。1个复杂问题概要：客户反馈问题与内部根本原因认定存在分歧。具体情况：客户认为某功能异常属设计缺陷，我方归因为试产阶段工装调试偏差，双方对责任归属和整改范围未达成一致。解决思路：启动客户质量协同机制，组织三方（我方质量、研发、客户质量）联合复现与根因分析，以客户实际使用环境测试数据为裁决依据，并将共识结论写入转产风险备忘录，经双方质量负责人签字后方可进入转产决策流程。</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>新产品质量</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>NPI质量策划</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>转产准入条件</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>在新产品导入的PVT阶段，质量阀点评审发现某关键芯片的供应商变更未经设计确认，但该芯片已贴装在全部试产整机中且功能测试合格。此时距离量产启动只剩3天，你会如何统筹决策是否放行？请简述你的判断逻辑、必须验证的动作及跨部门协同的关键节点。</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>严格依据NPI质量策划中质量阀点评审的准入原则，该变更未履行设计确认即进入PVT属重大流程越权，不满足质量放行前提；必须立即冻结放行动作，同步启动变更合规性追溯与风险再评估；核心验证动作包括：核查变更申请单及设计签核记录、复测关键功能与边界工况、开展短期可靠性摸底（如高低温循环）、确认新旧供应商物料批次可追溯性；跨部门协同必须拉通研发、采购、工艺、生产计划四方，在24小时内召开紧急质量阀点重评会议，由先期质量负责人牵头输出放行建议并升级至项目质量总监决策。</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>常见处理路径有四种：一是直接否决放行，适用于变更影响范围不明或设计未留痕场景，但易导致项目交付中断；二是有条件放行，需基于历史数据证明该芯片属成熟料号且新供方已通过PPAP，但若缺乏设计背书仍存合规风险；三是启动快速设计补签+补充验证双轨并行，时效性强但依赖研发响应速度；四是启用备选方案切换，仅当原设计BOM存在替代路径且已验证时可行。当前只剩3天，最管用的是第三种——以设计补签为刚性前提，同步开展最小成本验证（如抽样加速老化+关键功能压力测试），所有动作须在质量阀点评审闭环清单中逐项签字确认，确保过程可审计。</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：设计团队以‘功能达标即等效’为由拒绝补签。具体情况：研发认为测试结果无差异，主观跳过变更管控流程。解决思路：引用企业NPI质量门禁管理规范第4.2条，明确供应商变更属于设计输入变更，必须经DFMEA更新及设计负责人书面批准，质量工程师有权否决未闭环的阀点。1个复杂问题概要：新旧供应商芯片存在微小参数漂移，但当前验证未覆盖长期老化后失效模式。具体问题：功能测试合格不能代表6个月寿命期内无早期失效率上升风险。解决思路：联合可靠性工程师采用加速退化试验模型进行外推评估，并将结果纳入质量阀点风险评级矩阵，若风险等级≥R3，则要求延迟放行并启动客户沟通预案。</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>新产品质量</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>NPI质量策划</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>质量阀点评审</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>请简单说说，反应计划里‘隔离’这个动作，通常是指把哪类物品单独存放？</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>在控制计划的反应计划中，‘隔离’这个动作，特指将尚未通过质量判定、状态未明的可疑品或已确认不合格的新产品样件、试制件、首批量产件等，从正常物料流中物理分开并单独存放。</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>实际工作中常用四种隔离方式：一是按批次隔离，适用于小批量试制阶段，能快速锁定问题范围但易遗漏混批风险；二是按工序节点隔离，在过程巡检或首件确认异常时启用，时效性强但需同步暂停下游作业；三是按特性维度隔离，比如针对尺寸超差、外观缺陷或功能失效分别设区，便于后续分类分析，但对现场标识和人员识别能力要求高；四是按责任主体隔离，如供应商来料异常时在收货区划出专属隔离区，利于追溯与协同处置。当前消费电子通信智能设备制造业普遍采用‘工序节点+特性维度’组合方式，既保障响应速度，又支撑多维度根本原因分析，尤其适配新项目频繁变更、验证周期紧的特点。</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：隔离对象错判为合格品流入后道。具体情况是试制阶段因检验标准未同步更新，将存在潜在失效风险的新型号结构件误判放行。解决思路是建立隔离触发双校验机制——由过程质量工程师与先期质量工程师联合签字确认隔离必要性，并在MES系统中强制关联该批次的控制计划版本号与特殊特性清单。1个复杂问题概要：多个新品交叉试制时隔离区域被共用导致状态混淆。具体问题是同一隔离区内同时存放A项目外观件、B项目功能模组和C项目EMC整改样件，且无动态状态标签。解决思路是推行‘一物一码一区’动态隔离管理，每个隔离单元绑定唯一二维码，扫码实时显示所属项目、控制计划编号、判定状态及预计处置时限，由质量工程师每日班前核查并更新，确保新产品质量状态全程可视、可溯、可控。</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>新产品质量</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>控制计划制定</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>反应计划理解</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>在新产品导入初期，控制计划中对关键尺寸的检验频次通常设定为全检，这是基于什么基本质量原则？请简述。</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>这是基于‘预防为主、早期拦截’的质量基本原则。在新产品质量策划阶段，由于过程能力尚未稳定、人员操作熟练度不足、设备参数未充分验证、工装夹具处于磨合期，关键尺寸存在较高变异风险，必须通过全检实现100%风险识别与即时拦截，确保不合格品不流入下道工序或客户。</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>实际工作中有四种常用调整方式：一是基于首三批数据快速评估CPK后动态降频，适合量产节奏紧但供应商协同强的项目；二是按班次+批次双维度分层抽样，适用于多班倒且过程稳定性初步显现的情况，但若换型频繁易造成样本代表性不足；三是结合防错装置部署进度同步优化频次，稳妥但依赖跨部门响应速度；四是采用统计过程控制预判窗口期，在SPC初始控制图连续25点受控后启动频次评审。当前最管用的是第一种，因其兼顾时效性与数据驱动，符合消费电子通信智能设备行业快迭代、短周期的项目节奏，且能支撑PPAP提交所需的初始过程能力证据。</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：全检执行不到位导致漏检。具体情况是产线为赶试产进度，将全检简化为‘抽检+目视跳检’，造成某批次结构件关键装配孔位超差未被发现，后续组装出现批量干涉。解决思路是质量工程师须在控制计划签署前完成检验资源匹配性验证，包括工装检具数量、检验员排班、节拍适配性，并在试产启动会上联合工艺与生产明确‘全检不可替代’的红线要求。1个复杂问题概要：关键特性定义与客户要求存在理解偏差。具体问题是客户图纸标注的GD&amp;T公差带与内部控制计划中的关键尺寸项不完全对应，导致全检对象范围扩大或遗漏。解决思路是质量工程师须在APQP第二阶段即组织设计、工艺、客户质量三方开展特性矩阵对齐会，以客户PPAP包和SOR为唯一输入源，用特征管理表固化关键尺寸清单，并在控制计划版本变更时同步触发DFMEA更新评审。</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>新产品质量</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>控制计划制定</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>检验频次设定</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>某智能穿戴设备的电池装配工序控制计划中明确：若连续5台出现电池盖板间隙超差，须当场更换夹具并复测首件。请简单说说，为什么要求‘更换夹具’而不是仅重新调校或清洁现有夹具？</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>因为控制计划中的反应计划是基于过程失效模式风险等级设定的刚性动作，当连续5台发生同一关键特性超差时，表明当前夹具已超出统计受控状态，存在系统性偏差或磨损失效，必须执行根本性干预以阻断不合格流出。</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>在消费电子量产现场，常见应对方式有三种：一是仅清洁夹具，适用于异物嵌入导致的瞬时偏差，但无法解决夹具本体形变或定位销磨损；二是现场调校，适合夹具基准松动类问题，但调校精度依赖人员经验且无过程验证闭环，易掩盖真实失效；三是直接更换夹具，这是最可靠的选择，它规避了调校误差、人为判断偏差和验证滞后风险，符合智能穿戴产品高节拍、小批量、多型号切换下的快速响应要求，也便于后续开展夹具寿命分析与预防性维护策划。</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：操作员未更换夹具而选择自行调校，导致后续20台产品间隙持续超差。具体情况：调校后未执行首件复测即放行生产，且巡检未覆盖该时段批次。解决思路：立即停线追溯该时段所有产品，同步核查控制计划执行记录与首件签样单，对未按反应计划执行的行为纳入分层审核重点项，并在班前会重申反应计划的强制性与时效性要求。1个复杂问题概要：同一型号夹具在不同产线频繁触发更换，但新夹具使用不久又重复超差。具体问题：表面是夹具问题，实则暴露夹具设计公差与设备动态精度不匹配，或来料电池盖板尺寸批次波动未被上游过程监控识别。解决思路：联合先期质量与开发SQE启动夹具-工装-来料三维匹配分析，将此现象升级为变化点管理事件，推动更新夹具验收标准及来料关键尺寸SPC管控阈值。</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>新产品质量</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>控制计划制定</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>反应计划理解</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>为某款工业级手持扫码终端制定静电放电抗扰度测试方案时，如何确定接触放电和空气放电的电压等级及施加次数？请简述设定依据中需重点考虑的产品使用场景特征。</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>依据IEC 61000-4-2标准要求，结合该产品在汽车制造车间、物流分拣线、仓储作业等典型工况下的人员操作频次、环境温湿度、地面材质及防护装备使用情况，确定接触放电优先选用±4kV、空气放电±8kV；每点施加10次单脉冲，正负极性各5次。电压等级和次数设定须与产品实际暴露风险强度匹配，不得简单套用通用等级。</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>实践中常用三种调整策略：一是按主机厂配套要求直接采用其发布的EMC验收等级表，适用于已进入Tier1供应商体系的项目，但若终端用于二线物流承运商场景则可能过度测试；二是参照同类竞品量产机型的历史测试数据反推，适用于快速立项项目，但若竞品未覆盖金属货架密集环境则易低估空气放电风险；三是联合工艺与客户质量团队开展现场人因观察+环境测量，识别高频触碰点与典型放电距离，该方法时效性略低但适配性最强，尤其适合新导入产线或变更作业模式的项目。当前最管用的是第三种，因其能支撑质量工程师在开发早期就识别出如‘戴棉质手套扫描金属托盘’这类真实干扰场景。</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：测试电压等级被研发部门直接沿用消费类手持设备标准（如接触±2kV），导致量产前客户审核不通过。具体情况：该终端用于整车厂总装线，操作员频繁触摸金属工装台后立即操作设备，实际静电积累远超消费场景。解决思路：质量工程师须在APQP阶段牵头组织使用场景FMEA，将‘金属环境+高湿度+无防静电腕带’作为关键输入，推动测试等级升级并完成内部PPAP文件更新。1个复杂问题概要：同一型号终端需同时满足主机厂与第三方物流客户的差异化静电等级要求。具体问题：前者要求接触±6kV（对应洁净装配区），后者仅接受±4kV（对应常温常湿仓库）。解决思路：质量工程师应主导制定分级测试矩阵，在设计冻结前明确不同配置版本对应的测试边界，并在供应商质量管理协议中固化验证责任归属，避免量产交付时出现验收分歧。</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>可靠性验证</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>可靠性测试策划</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>测试条件设定</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>对新量产的智能音箱做ESD静电放电测试，为什么需要多台样机而非仅1台？请简述基本依据。</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>因为单台样机无法代表量产批次的一致性水平，ESD测试属于破坏性可靠性验证，需通过多台样机暴露工艺波动、装配差异和元器件批次离散性带来的失效风险，确保测试结论具备统计代表性，支撑量产放行决策。</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>实践中常用三种样本策略：一是按AQL抽样原则设定最小台数，适用于已有历史数据且供应商过程能力稳定时，但若新产线尚未积累过程数据，易低估风险；二是采用分层取样法，从不同生产班次、不同模组供应商、不同组装工站各取样，能有效覆盖变化点，但需提前识别关键过程变量，否则分层依据不充分反而降低有效性；三是结合FMEA高风险项定向加测，例如对USB接口、麦克风阵列等ESD敏感区域对应样机重点覆盖，时效性强且聚焦质量控制要点，特别适合新项目量产初期资源受限场景，是当前消费电子行业最常用且务实的做法。</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：测试中仅用1台样机通过，但量产后批量出现ESD失效。具体情况：该样机恰为当批一致性最好的个体，未暴露贴片偏移、屏蔽罩虚焊、接地铜箔压合不良等过程变异。解决思路：立即回溯首件及过程巡检记录，锁定当日关键变化点，启动小批量复测并同步开展产线过程审核，将样本策略从‘单点验证’升级为‘变化点驱动多台覆盖’。1个复杂问题概要：客户要求ESD测试通过率100%，但内部测试发现3台中有1台失效，是否允许放行？具体问题：该失效属偶发性接触放电失效，复测不可复现，且无明确根本原因。解决思路：暂停放行，组织先期质量与量产SQE联合开展失效模式溯源分析，同步评估该失效在用户真实使用场景下的发生概率与影响等级，基于风险矩阵输出有条件放行建议，并将该案例纳入后续PPAP文件中的可靠性测试样本策划说明中。</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>可靠性验证</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>可靠性测试策划</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>样本数量风险</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>在验证某款无线路由器的高温老化可靠性时，如果只测试2台样机，可能掩盖哪类质量问题？请简述。</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>仅用2台样机开展高温老化可靠性验证，无法覆盖制造过程中的批次性变异和装配离散性风险，极易掩盖由来料批次差异、产线工艺波动、作业人员操作不一致等引起的系统性失效问题，导致可靠性结论缺乏统计代表性，不能支撑量产放行决策。</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>实践中常用四类调整方式：一是按产品复杂度和历史数据动态设定最小样本量，适用于已有同类产品失效数据库的新项目；二是采用分层抽样，按关键物料供应商、不同产线班次、组装工位等维度拆解抽样，适合多工厂或多班次协同量产场景；三是引入加速退化数据建模辅助判断，但需已建立该型号的失效物理模型，否则易误判；四是结合早期市场返修数据反向校准验证强度，适用于已上市迭代型号。当前最管用的是分层抽样法，它在不显著延长周期前提下，能快速暴露过程控制薄弱环节，符合消费电子行业小批量快迭代的质量策划节奏。</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：测试后无失效，直接判定通过。具体情况：2台样机全部通过72小时高温老化，团队据此签署可靠性放行意见，但量产后出现批量Wi-Fi模块间歇断连。解决思路：立即回溯验证方案评审记录，核查是否完成过程FMEA中‘热应力导致射频前端焊点微裂’这一高风险项的样本覆盖评估，并启动对首三批来料批次号、SMT炉温曲线记录、AOI检测覆盖率的交叉稽查。1个复杂问题概要：客户审核质疑样本量依据不足。具体问题：主机厂质量代表指出该验证未体现IEC 61508或Telcordia GR-63-CORE中关于置信度与失效数的匹配逻辑。解决思路：不直接引用标准条款，而是调取本司近3年同平台路由器高温失效TOP3模式清单及对应发生批次的过程控制能力指数，用实际过程稳定性数据反推本次验证的工程合理性，聚焦说明‘2台’是作为过程受控状态下的风险探针，而非最终可靠性承诺值。</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>可靠性验证</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>可靠性测试策划</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>样本数量风险</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>请简单说说ESD测试中，人体放电模型通常模拟的是哪种日常操作场景？</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>人体放电模型主要模拟的是作业人员在产线装配、检验、包装或物流转运等环节中，未规范佩戴防静电装备时，用手直接接触电子部件或整机外壳所引发的静电放电过程。</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>在实际质量管控中，常用三种作业方法来应对该场景：一是将HBM测试点位与产线高频触碰区域（如接口区、按键区、金属边框）强关联，确保测试覆盖真实风险面，适用于新机型导入阶段；二是结合人因工程观察法，在量产前对组装工位开展30分钟以上现场跟岗记录，识别典型徒手操作动线，避免测试点设置脱离实际，但若仅依赖单次观察易遗漏夜班或替岗人员操作差异；三是将HBM测试结果与客户投诉中‘开箱即失效’‘上电无反应’类问题做根因回溯匹配，反向验证模型代表性，该方法时效性强且闭环直接，但需依赖完整的售后数据归集机制支撑。</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：HBM测试通过但量产初期出现批量静电损伤。具体情况：测试仅覆盖标准板级器件引脚，未覆盖整机状态下结构件耦合放电路径，导致外壳缝隙处静电耦合至内部PCB未被检出。解决思路：在先期质量策划阶段，联合结构和硬件工程师，基于整机三维模型识别高风险静电耦合界面，将HBM施加点延伸至结构件与PCB临近区域，并纳入DFMEA特殊特性清单。1个复杂问题概要：同一型号产品在不同代工厂HBM失效率差异显著。具体问题：A厂使用全金属托盘+离子风机，B厂采用普通塑料周转箱且无局部消散措施，导致人体带电状态建模基础不一致。解决思路：以量产SQE身份牵头制定《ESD过程基准确认清单》，明确各厂必须统一执行的人体接地电阻实测频次、环境温湿度监控阈值及周转器具表面电阻验证方法，并纳入PPAP提交文件强制审核项。</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>可靠性验证</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>合规验证理解</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>ESD测试理解</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>开展某款车载摄像头模组的温度循环测试时，若只用1颗样品，会对失效结论的可信度产生什么影响？请简述。</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>仅使用1颗样品开展温度循环测试，无法支撑对车载摄像头模组批量生产条件下失效模式、失效机理及失效率水平的可靠判断，违背IATF16949对可靠性验证中样本代表性与统计置信度的基本要求，直接影响该模组在开发阶段质量放行决策的严谨性。</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>实际工作中有四种常见应对方式：一是沿用最小样本量表（如MIL-STD-105E或AIAG APQP指南推荐的3～5颗），适用于设计验证初期快速暴露明显缺陷，但若样品本身存在批次异常则易误判；二是按威布尔分布预估所需样本数并结合加速因子反推，适用于已有同类产品历史数据支撑的项目，但新平台缺乏基线数据时适用性差；三是采用分层抽样策略，从不同工艺段、不同供应商批次中各取1颗组成最小有效样本组，兼顾过程变异覆盖，需依赖前期PFMEA识别的关键变化点信息；四是联动供应商开展联合验证，由主机厂与模组厂同步执行平行测试，提升结果交叉验证强度。当前车载摄像头项目普遍采用第三种方式，在保证时效前提下兼顾过程变异覆盖和资源可及性。</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：测试后仅1颗样品失效，但无其他样品佐证是否属偶发性单点异常。具体情况：该失效未复现在后续小批量试产中，也未被DFMEA识别为高风险模式，导致开发团队误判为偶发事件而未关闭风险。解决思路：立即回溯该样品的制造履历、来料批次、工艺参数及测试环境记录，结合先期质量策划中定义的特殊特性清单，组织跨功能小组进行失效再现性评估，并将结论纳入量产前质量评审输入。1个复杂问题概要：在PPAP提交节点临近时，因样品交付延迟被迫以1颗完成温度循环测试。具体问题：该结果被客户质量部门质疑，影响PPAP批准进度，并触发客户8D流程启动。解决思路：主动向客户质量团队同步测试局限性说明，同步提供该样品的全流程质量追溯信息、供应商过程能力证据及已规划的量产批次加严验证方案，将单次测试结果定位为‘风险提示项’而非‘放行依据’，推动客户认可分阶段验证路径。</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>可靠性验证</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>可靠性测试策划</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>样本数量风险</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>消费电子整机在做人体模型静电放电测试时，标准要求接触放电±8kV不出现功能异常，但实测中发现同一型号不同批次产品通过率波动较大。请简述你认为最需要核查的三个与测试实施直接相关的现场执行因素。</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>第一层：需核查静电放电测试执行过程中测试设备校准状态是否有效、放电枪头与被测产品接触方式是否符合标准规定的接触压力与接触角度、测试环境温湿度是否持续满足IEC 61000-4-2要求的15℃～35℃、30%～60%RH范围。</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>第二层：针对设备校准，应采用最新版CNAS认可实验室出具的周期校准报告+每日开机前功能验证双轨核查，避免仅依赖过期校准证书；接触方式核查需结合测试员操作录像回溯与触点痕迹比对，单纯靠目视确认易漏判枪头氧化或倾斜；环境监控须调取测试全程连续记录数据而非仅抽查单次读数，因ESD敏感度对湿度突变极为敏感，短时超差即导致结果漂移。三者中，接触方式核查时效性最强、问题暴露最直接，是首批必查项。</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>第三层：1个异常情况概要——测试员未按规程更换放电枪头导电弹簧片。具体情况：弹簧片磨损后接触电阻增大，导致实际放电能量衰减，同一批次产品在不同测试员间出现通过率差异。解决思路：将弹簧片更换纳入测试工装点检表，绑定扫码换件记录，并与测试系统自动关联放电参数日志。1个复杂问题概要——多工位共用一台ESD发生器且未实施放电路径独立接地管理。具体问题：相邻工位测试时地电位耦合导致放电波形畸变，造成部分批次产品在A工位合格、B工位失效。解决思路：推动测试区域实施单工位独立接地桩配置，加装高频阻抗检测模块实时监控接地有效性，并将接地状态作为测试启动前置条件写入MES系统控制逻辑。</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>可靠性验证</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>合规验证理解</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ESD测试理解</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>某款蓝牙耳机在功能测试中，所有单机测试项均合格，但整机包装后抽检发现10%的耳机无法与手机稳定配对。请简述，这种批量出现的配对异常，最可能源于哪一环节的误测或漏测？</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>该问题最可能源于系统级功能测试环节的漏测，即未在模拟真实交付状态（含完整包装、堆叠、运输振动、电磁屏蔽环境）下开展蓝牙配对稳定性验证。</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>质量工程师需从测试覆盖维度识别三类常见调整路径：一是补做包装态系统测试，适用于量产爬坡期快速拦截，但若未同步更新检验标准则易造成后续批次重复漏判；二是将包装后静置+温湿度循环作为必测工况纳入功能测试用例库，适用于新项目开发阶段，但若未与工艺部门协同确认包装材料导电性影响则可能低估射频衰减风险；三是引入分层审核机制，在包装线末位设置蓝牙连通性抽测点，时效性强且贴近过程控制，但依赖操作员执行规范性，若缺乏防错校验易流于形式。当前场景下，最管用的是第二类方法，因其能从根本上将包装态干扰纳入质量策划基线，符合先期质量方向对特殊特性识别和失效预防的要求。</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：包装材料金属镀层或铝箔衬垫导致蓝牙天线信号衰减被长期忽略。具体情况：测试仅在裸机状态下进行，未识别包装结构对2.4GHz频段的屏蔽效应，造成10%批次性失效。解决思路：联合包装工艺与射频工程师开展包装态EMC摸底测试，将包装材料透波率纳入来料质量协议，并在PPAP文件中明确包装态功能验证要求。1个复杂问题概要：配对失败呈现非均匀分布，部分箱体集中失效。具体问题：仓储堆叠高度差异引发不同压力下壳体微变形，导致天线馈点接触阻抗漂移，单机测试无法复现该应力耦合失效。解决思路：在量产前质量策划阶段，将运输仓储典型工况纳入系统测试边界条件，通过DOE方式设计堆叠压力+温湿度组合验证方案，并将结果固化为分层审核中的关键控制点。</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>系统测试质量</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>功能测试质量</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>误测漏测风险识别</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>某工业级边缘计算设备在完成IEC 61000-4-2标准ESD测试后交付客户，半年内因静电导致的启动失败率上升至千分之三。追溯发现所有失效设备均发生在同一产线批次，且该批次PCB在回流焊后增加了局部三防漆涂覆工艺。你如何从ESD路径完整性角度分析该工艺变更的影响？请说明三防漆物理特性与静电泄放机制的冲突本质及验证切入点。</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>作为质量工程师，需立即启动变化点管理流程，将该三防漆工艺新增识别为关键过程变更，依据IATF16949条款8.5.6开展变更影响评估；聚焦ESD路径完整性这一合规验证要求，确认该工艺是否覆盖了原设计定义的ESD泄放路径关键节点，如接地焊盘、屏蔽层连接点、接口端子附近的参考地铜箔等；同步核查该批次PPAP文件中是否包含针对此工艺调整的ESD补充验证记录。</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>常用作业方法有四种：一是组织跨职能小组开展DFMEA/PEMEA联动评审，适用于设计与制造协同充分的场景，但若缺乏硬件工程师深度参与易流于形式；二是调取该批次首件检验及过程审核记录，重点比对三防漆涂覆范围与ESD设计图纸的一致性，时效性强但依赖现场记录完整性；三是推动供应商提供三防漆材料物性报告并核验其表面电阻率是否超出10⁹Ω/sq限值，适合来料管控成熟的企业，但若仅依赖COA而未做实测则存在风险；四是发起小批量复测——在产线抽取同工艺样品补做IEC61000-4-2空气放电测试，最贴近真实失效逻辑，是当前最管用的方法，兼顾时效性与证据力。</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：三防漆意外覆盖ESD保护器件接地焊盘。具体情况：目视检查难发现微米级覆盖，导致TVS或ESD二极管无法有效泄放电荷，表现为偶发性上电失败。解决思路：在过程巡检中增加‘关键ESD路径区域’专项点检项，使用带放大功能的手持式红外热像仪辅助识别涂覆异常，并将该点检纳入分层审核清单。1个复杂问题概要：三防漆与PCB阻焊层界面产生静电驻留。具体问题：两种绝缘材料叠层后形成电荷陷阱，在温湿度波动下缓慢释放干扰MCU复位电路。解决思路：联合先期质量与客户质量团队，将该现象纳入整车与产品评价中的环境应力可靠性专项评价，通过加速湿热循环+ESD组合试验复现并锁定失效阈值，输出面向量产的过程控制红线。</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>可靠性验证</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>合规验证理解</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>ESD测试理解</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>在过程审核中发现某工位未按要求对关键尺寸做首件检验，但当天所有产品最终检验都合格，这通常应判定为什么级别问题？请简单说说。</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>该问题应判定为严重不符合项。依据IATF16949标准及汽车行业过程审核通用实践，首件检验是针对关键特性实施的强制性防错控制措施，其缺失直接导致过程失控风险未被识别，属于对质量管理体系有效性构成实质性削弱的情形，不因最终检验结果合格而豁免其严重性。</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>实际工作中有四种常见处理方式：一是直接按体系条款判定为严重不符合，适用于该工位无替代监控手段、关键尺寸无过程能力数据支撑的情况，时效快但需同步启动遏制；二是降级为一般不符合，仅在已验证该工序具备稳定的过程能力、且当日有完整SPC监控记录并受控时才适用，否则易掩盖系统漏洞；三是作为观察项记录，仅限于首次轻微偏离且有即时纠正证据、同时该特性在近三个月内无任何波动趋势，但消费电子通信智能设备行业因变更频繁、交付节奏快，此做法风险高；最稳妥的是按严重不符合闭环，同步开展变化点排查和分层审核加频，既满足审核严谨性，又契合该行业对过程防错刚性要求高的特点。</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：审核员因产品终检合格而主观弱化问题等级。具体情况：现场看到检验报告全绿，误判‘没出问题’，忽略首件缺失意味着过程稳定性未经验证，尤其在消费电子行业高频换线、多型号共线场景下，一次首件漏检可能覆盖多个变更批次。解决思路：坚持‘控制措施失效即严重’原则，核查该工位最近三次换型或参数调整是否均执行首件，结合分层审核记录交叉验证。1个复杂问题概要：同一问题在多个工位重复发生。具体问题：三个不同产线的同类工位均未执行关键尺寸首件，暴露防错机制设计缺陷或作业指导书未与MES系统校验联动。解决思路：升级为体系层面问题，推动质量体系工程师牵头修订《首件管理程序》，嵌入工单触发自动弹窗提醒与电子签名强制留痕，并纳入过程审核检查表的必查项。</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>质量体系审核</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>过程审核理解</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>审核问题分级</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>过程审核时看到产线正在使用已过期的作业指导书，且该文件涉及安全操作步骤，这属于哪一类问题等级？请简述。</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>这属于严重不符合项。依据IATF16949标准及消费电子通信智能设备制造业过程审核通用分级规则，当作业文件失效且直接影响人员安全、产品安全或法规符合性时，无论是否已造成实际后果，均应判定为严重不符合。</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>在实际审核中，有四种常见处理路径：一是直接升级为严重不符合并立即叫停相关工序，适用于安全条款明确、风险不可控场景，但若未同步启动应急沟通机制，易引发产线停工争议；二是先标记为待确认严重项，结合现场风险评估矩阵快速验证当前操作是否实际偏离安全要求，适合变更影响尚不清晰但文件确已过期的情形，但若评估流于形式则可能低估风险；三是联动变更管理流程追溯过期原因，判断是文件管控失效还是临时授权缺失，适用于体系成熟度较高、有完整变更闭环机制的企业，但在新项目导入期或组织架构调整阶段容易因职责断点导致追溯失效；四是按客户特殊要求（如华为、苹果供应链质量协议）直接触发升级通报机制，适用于已知客户对文件时效性有明文强约束的场景，最契合消费电子行业高频迭代、强合规导向的特点，时效性强且责任界面清晰。</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：审核员发现文件过期但产线声称‘技术部口头同意沿用’。具体情况：无书面授权记录，也无临时替代方案评审证据。解决思路：立即核实口头授权是否纳入变更管理受控范围，若未受控则仍属严重不符合，并推动建立‘紧急沿用’的最小化审批模板与留痕机制。1个复杂问题概要：同一份作业指导书在多个工位版本混用，部分工位用过期版、部分用新版，且安全步骤存在差异。具体问题：无法单点判定责任归属，涉及文件分发、培训、目视化管理、班组长履职等多个过程接口。解决思路：以分层审核为抓手，从文件控制流程切入，调取最近三次分发记录、培训签到与考核结果、工位目视化标识照片及班前会记录，定位过程断点，聚焦过程所有者而非单点执行人进行闭环整改。</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>质量体系审核</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>过程审核理解</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>审核问题分级</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>在质量整改闭环中，判断一个问题是否真正关闭，最直接的依据是什么？请简单说说。</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>最直接的依据是整改措施已在实际生产或交付场景中稳定运行至少一个完整批次（或一个自然生产周期），且该问题对应的质量特性经独立验证确认未再复发，同时相关证据已完整归档至质量管理系统并完成跨职能签字确认。</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>实践中常用四种验证方式：一是基于量产节拍下的连续三批抽样验证，适用于过程参数类问题，但若批次间隔长或产量低则时效滞后；二是客户现场使用反馈回溯，对售后类问题敏感度高，但存在信息延迟和归因偏差风险；三是分层审核中嵌入专项查证，能快速穿透执行层，但依赖审核员专业深度；四是系统自动抓取防错装置触发记录或SPC控制图稳定性数据，客观性强、响应快，但需前期数字化基础支撑。当前消费电子通信智能设备制造业普遍优先采用‘系统数据+现场复测+客户签认’三重交叉验证，兼顾时效性与可追溯性。</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：整改措施已实施但问题在后续批次中偶发重现。具体情况：表面看措施已落实、记录齐全，但根本原因未消除，如某主板贴片虚焊问题仅靠加强AOI检出而未优化回流炉温区曲线。解决思路：必须回归问题关闭判定本质——不是看动作是否做完，而是看失效模式是否真正被阻断；需调取近30天该工位首件/巡检/终检数据趋势，并比对措施实施前后同类缺陷逃逸率变化。1个复杂问题概要：客户要求关闭的问题，内部验证达标但客户端仍拒签。具体情况：主机厂质量代表以‘未覆盖全部变型配置’为由不认可供应商8D闭环。解决思路：立即启动配置矩阵完整性核查，联合研发与项目管理梳理所有BOM变型清单，针对性补做关键配置项验证，并以客户认可的格式同步提交配置覆盖声明与实测证据包，而非仅重复原有验证报告。</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>质量体系审核</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>整改有效性验证</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>问题关闭判定</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>请简述：在电子制造中，AQL抽样检验时，'严重缺陷'通常指哪类问题？请举一个常见例子。</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>在电子制造的质量检验工作中，AQL抽样检验中的‘严重缺陷’是指可能直接导致产品丧失基本功能、引发安全风险、违反强制性法规要求或造成客户拒收的缺陷类型。这类缺陷不接受让步放行，一旦检出即触发整批拒收。</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>实际作业中，质量工程师常采用三种判定方式：一是依据企业已批准的《缺陷分类标准》对照表快速归类，适用于常规型号且标准版本稳定的场景，但若新项目未及时更新标准则易误判；二是结合客户特殊要求清单（如华为/苹果的CSR）逐条核对，适用于高要求客户交付前验证，但耗时较长且需跨部门确认；三是组织跨职能小组（含研发、工艺、客服代表）开展缺陷影响评估会，适用于首单试产或变更后首次检验，能动态识别潜在严重性，但决策周期长、资源依赖强。当前量产阶段最常用的是第一种方式，前提是标准文件已同步至一线检验系统并完成最新版本培训。</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：检验员将某款智能手表充电接口处轻微划伤误判为严重缺陷。具体情况：该划伤仅影响外观，无结构损伤、不影响防水密封及插拔功能，但检验员未查阅最新版《消费类智能穿戴产品缺陷分级指南》中关于外壳非功能区表面缺陷的放宽条款。解决思路：立即启动现场判定复核机制，由班组长调取当期有效标准文件与实物比对，并同步在当日质量晨会中重申‘功能面与非功能面’的区分逻辑。1个复杂问题概要：同一缺陷在不同客户标准下归属不一致。具体问题：某Type-C接口接触不良，在国内主机厂标准中属严重缺陷（因整车通信模块依赖该接口），但在出口海外消费电子客户的验收标准中被列为轻微缺陷。解决思路：质量工程师须在项目早期就梳理客户差异化要求，在AQL抽样方案中设置双轨判定规则，并在检验指导书里嵌入客户标签标识和对应缺陷等级映射表，确保检验执行不混淆。</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>质量基础判定</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>缺陷判定规则</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>判定标准理解</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>请简述，为什么充电接口的金属触片平整度会影响整机功能可靠性？</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>作为质量工程师，在消费电子通信智能设备制造业中识别关键质量特性时，需将充电接口金属触片的平整度判定为影响整机功能可靠性的关键质量特性。该特性直接关联电气接触稳定性与插拔耐久性，属于开发阶段必须管控的特殊特性，也是量产过程巡检、首件确认及供应商来料检验的核心监控项。</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>在实际工作中，常用四种作业方法识别和验证该特性的关键性：一是结合DFMEA分析输出的高风险失效模式（如接触不良导致充电中断），反向锁定触片平整度为关键控制项；二是依据客户投诉数据聚类，若批量出现‘偶发无法充电’问题且复现于同一接口批次，则快速将其列为优先识别对象；三是通过分层审核中对组装线末位工位的触片压入力与形变目视比对，辅助判断平整度失控趋势；四是调用PPAP文件中的特性矩阵表，核查该参数是否已被标注为安全/法规相关特性。其中，DFMEA反推法最适用于新项目先期质量策划阶段，而客户投诉聚类法在量产阶段时效性最强、闭环路径最短。</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：量产过程中发现多台样机在老化测试后期出现间歇性充电失败。具体情况：触片平整度超差未被首件检验拦截，因检测标准未明确公差带宽与测量点位，导致仅抽检中心点而漏判边缘翘曲。解决思路：立即冻结该批次接口来料，同步修订检验作业指导书，增加三点测量要求及翘曲量具校准频次，并将该变异纳入供应商8D整改的变更管控清单。1个复杂问题概要：跨供应商替换触片物料后整机可靠性下降但无明确失效复现。具体问题：两家供应商均满足图纸公差，但微观波纹度与弹性模量差异引发插拔循环后平整度衰减速率不同，现有质量协议未约定动态平整度保持能力。解决思路：联合开发SQE与先期质量团队，在新物料准入前补充定义‘插拔50次后平整度保持率’为新增关键质量特性，并写入供应商质量协议与PPAP提交清单。</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>质量基础判定</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>质量对象识别</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>关键质量特性识别</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>在电子厂对一批新到的USB-C连接器做来料检验时，按标准选用II级一般检验水准和AQL为0.65%，请问这个AQL数值具体代表什么意思？请简单说说。</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>AQL为0.65%是指在来料抽样检验中，质量工程师可接受的该批USB-C连接器最差的过程平均不合格品率上限；当供应商长期供货的实际不合格率不高于此值时，该抽样方案有较高概率判定为合格并予以接收。</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>在消费电子来料检验场景中，质量工程师通常会结合三类作业方法灵活应用：一是直接沿用客户或企业内控标准规定的AQL值，适用于已有成熟合作历史、过程能力稳定的供应商，但若供应商近期发生制程变更或换线，则可能掩盖真实风险；二是根据产品功能安全等级动态调整AQL，比如对影响充电协议握手或数据传输稳定性的关键尺寸项，临时收紧至0.25%，但需同步更新检验指导书并完成跨部门确认，否则易引发采购或产线执行偏差；三是将AQL与检验严格度联动，在连续多批接收后自动切换至加严检验，反之则放宽，这种做法在USB-C这类高一致性要求的接口件上能平衡效率与风险，但前提是检验记录完整且系统支持自动触发逻辑。当前USB-C连接器属通用高速接口件，功能失效直接影响终端用户体验和客诉率，因此优先采用客户协议锁定的0.65%并配套II级检验水准，兼顾识别力与检验成本。</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：供应商实际来料不合格率已升至0.8%，但因抽样随机性仍被判定接收。具体情况是连续两批USB-C插拔寿命测试未达标，但AQL抽样未覆盖该特性，仅抽检外观与尺寸。解决思路是立即启动分层审核，核查该AQL是否涵盖关键功能特性，同步在来料检验规范中将插拔寿命列为必检项目，并推动SQE介入供应商过程能力再评估。1个复杂问题概要：同一供应商不同批次USB-C连接器混用不同电镀工艺，导致AQL统一设定下无法区分工艺变异带来的批次间质量波动。具体问题是AQL 0.65%基于历史数据设定，但新工艺导入未触发检验方案重评。解决思路是建立供应商变更响应机制，凡涉及材料、工艺、模具等关键变更，必须由开发SQE牵头组织检验方案适配性评审，并在来料检验作业指导书中明确工艺标识核验与抽样分组要求。</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>检验抽样基础</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>AQL抽样检验</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>抽样水准理解</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>客户投诉问题后，8D报告中的‘D4根本原因分析’这一步，主要目的是什么？请简单说说。</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>D4根本原因分析的主要目的，是准确识别导致客户投诉发生的、可验证的、与制造过程或质量系统直接相关的真正原因，而不是表面现象或主观猜测，为后续制定有效纠正措施提供唯一可靠依据。</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>在消费电子通信智能设备制造业中，质量工程师开展D4时常用四种方法：一是鱼骨图+5Why组合分析法，适合多环节交叉问题，如PCBA功能失效涉及设计、来料、SMT工艺三方面，但若团队经验不足易陷入归因发散；二是故障树（FTA）简化版逻辑推演，适用于整机DOA类重复性失效，需有明确失效路径支撑，否则易忽略人为或系统性因素；三是对比分析法（OK/NG件横向比对），对结构件外观不良、连接器插拔力异常等物理类问题响应快、证据直观，但对软硬件耦合类问题覆盖不全；四是跨职能数据交叉验证法，即同步调取制程SPC、测试日志、供应商批次记录和客户使用场景信息，时效性强且闭环性好，是当前CQE岗位最常用也最推荐的方式，尤其适配客户反馈时间紧、责任界面复杂的特点。</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：根本原因被锁定为‘操作员未按作业指导书执行’。具体情况：实际是作业指导书本身未覆盖新导入的双面BGA器件返修温控要求，属文件缺陷而非人为失误。解决思路：立即回溯D4过程中是否验证了标准文件的适用性与版本有效性，强制将‘标准文件完整性’纳入D4原因验证 checklist。1个复杂问题概要：客户投诉的功能间歇性失效，在内部复现率低于5%，且无明确失效样品。具体问题：无法通过常规检测手段锁定稳定触发条件，导致D4陷入‘可能原因过多、验证成本过高、结论难共识’僵局。解决思路：联合研发和测试部门启动‘客户真实使用场景建模’，基于客户报修数据还原典型工况组合（如特定温湿度+多任务并发+低电量），在实验室搭建轻量级场景模拟平台，聚焦验证高概率耦合因子，避免泛泛排查。</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>客户质量管理</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>客诉问题闭环</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>客户8D回复</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>某消费电子整机厂对一批12000台智能手表主板执行来料AQL抽样检验，标准为AQL 0.65%，正常二次抽样方案。首轮抽检发现1个功能失效（严重缺陷），按规则进入第二轮抽样；第二轮又发现1个焊接虚焊（严重缺陷）。该物料处于新供应商导入阶段，且前两批已出现3次同类虚焊导致产线停线。请简述你对该批次的接收判定结论、核心判定依据，并说明此时必须立即协调的两个关键动作及其紧迫性理由。</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>该批次应判定为拒收。核心判定依据是：在AQL 0.65%的正常二次抽样方案下，两轮累计发现2个严重缺陷，已超出该方案允许的接收上限；同时，严重缺陷不适用放宽检验，且新供应商导入阶段默认执行加严检验，实际判定须以更严格规则为准。</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>实践中存在四种常见处理路径：一是严格按抽样表判定拒收，适用于供应商质量基础薄弱、历史问题未闭环的场景，但若机械执行可能延误试产节奏；二是启动MRB紧急评审，适用于缺陷可隔离返工且风险可控时，但需同步验证返工有效性，否则易造成隐性流出；三是临时加严至单次加严抽样并扩大样本量复验，适用于首件验证充分、过程记录完整的情况，但耗时较长，不适用于已发生产线停线的情形；四是结合历史数据触发供应商质量升级机制，这是当前最管用的做法——因前两批已三次虚焊致停线，表明系统性风险未受控，必须跳出单批次判定，转向供应商过程能力再评估。</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：抽样结果临界但历史问题频发。具体情况是两轮共2个严重缺陷恰好卡在二次抽样拒收边界，易被误判为‘可协商接收’。解决思路是立即调取该供应商近三批MRB记录与产线停线报告，以事实证据支撑拒收决定，避免质量让步成为惯例。1个复杂问题概要：AQL判定与供应链交付压力产生冲突。具体问题是采购或项目方以‘NPI进度紧张’为由要求特采，但虚焊属不可检出型风险，功能失效可能在老化或客户使用中突发。解决思路是质量工程师须联合PQE、SQE在2小时内输出《特采风险告知书》，明确标注失效模式、影响路径、责任边界及后续监控加严条款，确保决策留痕、风险可视、闭环可溯。</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>检验抽样基础</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>AQL抽样检验</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>批次接收判定</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>一款5G模组在老化测试后的信号接收灵敏度数据直方图显示：主峰集中但宽度异常窄，同时左右两侧各出现一个孤立、等高的小峰。已知该模组采用双供应商交替来料策略，且两个小峰位置恰好与两家供应商标称典型值一致。请说明该分布形态反映的核心质量风险，并指出在量产导入阶段应优先采取哪项具体动作来验证判断。</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>该直方图形态反映的核心质量风险是来料存在系统性供应商间差异，导致同一检验特性在量产批次中呈现双模态分布，表明过程未实现供应商间规格与性能的等效控制；在量产导入阶段应优先开展按供应商分层抽样并分别绘制直方图与CPK分析，验证两组数据是否各自符合规格且过程能力稳定。</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>常见作业方法有四种：一是仅做整体CPK计算，适用于单源或已确认供应商一致性的情形，但本题会掩盖双峰本质，误判过程能力充足；二是按来料批次号回溯分组分析，适合ERP/MES系统记录完整时，但若批次标签不准确或混批入库则易归类错误；三是依据供应商代码字段直接分层统计，时效高、可追溯性强，且适配当前双供应商交替策略下的数据结构，是当下最管用的方法；四是增加供应商标识字段后启动SPC实时监控，属于长效机制建设，但需系统改造周期，无法满足导入阶段快速验证需求。</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：供应商标识字段缺失或错标。具体情况：BOM或来料检验单中未记录供应商代码，或扫码录入时人工选择错误，导致分层分析基础失真。解决思路：立即核查最近三批来料检验原始记录与系统留痕，同步在IQC检验工单中强制增加供应商扫码校验环节。1个复杂问题概要：两供应商物料虽标称值不同但均在规格限内，且老化后性能漂移方向相反。具体问题：主峰窄说明单家供应商内部变异小，但双峰对称分布暗示两家物料老化行为存在固有差异，可能引发整机长期可靠性风险。解决思路：在NPI阶段推动SQE联合研发质量启动跨供应商的加速老化对比试验，并将结果纳入转量产准入评审清单，而非仅依赖单次老化后数据判定。</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>质量数据分析</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>质量统计工具</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>直方图应用</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>消费电子通信智能设备制造业</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>质量工程师</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
